--- a/LLM_Extraction_and_CrossCritique/interactive-table/runs/query-chosen-filters-columns_with_runs_pipeline1.xlsx
+++ b/LLM_Extraction_and_CrossCritique/interactive-table/runs/query-chosen-filters-columns_with_runs_pipeline1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="timings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,16 +455,6 @@
           <t>run_3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>run_4</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>run_5</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -476,8 +466,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Class of ICI": "PD1",
-    "Cancer type": "Non-Small Cell Lung Cancer"
+    "ICI Class": "PD-1",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -495,27 +485,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"ICI Class": "PD1", "Cancer Type": "NSCLC"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Name of ICI"}}</t>
+          <t>{"selected_filter": {"ICI Class": "PD-1", "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Name of ICI", "Column 7": "Class of ICI", "Column 8": "Monotherapy/combination", "Column 9": "Type of combination", "Column 10": "Control regimen"}}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "ICI Class": "PD1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Name of ICI"}}</t>
+          <t>{"selected_filter": {"ICI Class": "PD-1", "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Name of ICI", "Column 7": "Class of ICI", "Column 8": "Monotherapy/combination", "Column 9": "Type of combination", "Column 10": "Control regimen"}}</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "ICI Class": "PD1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"ICI Class": "PD1", "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"ICI Class": "PD1", "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Monotherapy/combination", "Column 8": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 9": "Control regimen", "Column 10": "Lines of treatment"}}</t>
+          <t>{"selected_filter": {"ICI Class": "PD-1", "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
     </row>
@@ -529,7 +509,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Monotherapy/combination": "Combination",
+    "Type of Therapy": "Combination Therapy",
     "Cancer Type": "Melanoma"
   },
   "selected_column": {
@@ -548,27 +528,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Clinical setting in relation to surgery", "Column 7": "Type of combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Clinical setting in relation to surgery", "Column 7": "Treatment regimen", "Column 8": "Name of ICI", "Column 9": "Type of combination", "Column 10": "Control regimen"}}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Clinical setting in relation to surgery", "Column 7": "Type of combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Monotherapy/combination"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Clinical setting in relation to surgery", "Column 7": "Treatment regimen", "Column 8": "Name of ICI", "Column 9": "Type of combination", "Column 10": "Control regimen"}}</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Clinical setting in relation to surgery", "Column 7": "Name of ICI", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Clinical setting in relation to surgery", "Column 7": "Treatment regimen", "Column 8": "Type of combination", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Clinical setting in relation to surgery", "Column 7": "Treatment regimen", "Column 8": "Type of combination", "Column 9": "Primary Endpoint", "Column 10": "Control regimen"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Clinical setting in relation to surgery", "Column 7": "Treatment regimen", "Column 8": "Name of ICI", "Column 9": "Type of combination", "Column 10": "Control regimen"}}</t>
         </is>
       </c>
     </row>
@@ -582,8 +552,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Class of ICI": "CTLA4 or any combination of CTLA4",
-    "Cancer type": "GEJ/Esophageal/GEJ"
+    "ICI Class": "CTLA-4 or any combination of CTLA-4",
+    "Cancer Type": "GEJ/Esophageal/GEJ"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -601,27 +571,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "ICI Class": "CTLA-4"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary endpoint", "Column 6": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "ICI Class": "CTLA-4"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Total sample size", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Lines of treatment"}}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "ICI Class": "CTLA-4"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary endpoint", "Column 6": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "ICI Class": "CTLA-4"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Total sample size", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Lines of treatment"}}</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "ICI Class": "CTLA-4"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Total sample size", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Type of Therapy", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "ICI Class": "CTLA-4"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Total sample size", "Column 7": "Name of ICI", "Column 8": "Clinical Setting in relation to surgery", "Column 9": "Type of combination", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "ICI Class": "CTLA-4"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Total sample size", "Column 7": "Name of ICI", "Column 8": "Monotherapy/combination", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "ICI Class": "CTLA-4"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Total sample size", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Lines of treatment"}}</t>
         </is>
       </c>
     </row>
@@ -635,9 +595,9 @@
         <is>
           <t>{
   "selected_filter": {
-    "Trial phase": "Phase 3",
-    "Monotherapy/combination": "Monotherapy",
-    "Cancer type": "Urothelial and Bladder"
+    "Trial Phase": "Phase 3",
+    "Type of Therapy": "Monotherapy",
+    "Cancer Type": "Urothelial and Bladder"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -655,27 +615,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Bladder", "Trial Phase": "Phase 3", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Bladder", "Trial Phase": "Phase 3", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Control regimen", "Column 8": "Follow-up duration for primary endpoint(s) in months [Overall]", "Column 9": "Follow-up duration for primary endpoint(s) in months [Rx]", "Column 10": "Follow-up duration for primary endpoint(s) in months [Control]"}}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Bladder", "Trial Phase": "Phase 3", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Lines of treatment"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Bladder", "Trial Phase": "Phase 3", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Control regimen", "Column 8": "Follow-up duration for primary endpoint(s) in months", "Column 9": "Total sample size", "Column 10": "Lines of treatment"}}</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Bladder", "Trial Phase": "Phase 3", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Total sample size", "Column 8": "Follow-up duration for primary endpoint(s) in months [Overall]", "Column 9": "Follow-up duration for primary endpoint(s) in months [Rx]", "Column 10": "Follow-up duration for primary endpoint(s) in months [Control]"}}</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Bladder", "Trial Phase": "Phase 3", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months", "Column 6": "Primary Endpoint", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Total sample size", "Column 10": "Lines of treatment"}}</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Bladder", "Trial Phase": "Phase 3", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Monotherapy/combination", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Bladder", "Trial Phase": "Phase 3", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Control regimen", "Column 8": "Follow-up duration for primary endpoint(s) in months", "Column 9": "Total sample size", "Column 10": "Lines of treatment"}}</t>
         </is>
       </c>
     </row>
@@ -689,8 +639,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Clinical setting in relation to surgery": "Adjuvant",
-    "Cancer type": "NSCLC"
+    "Clinical Setting": "Adjuvant",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -706,27 +656,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting in relation to surgery": "Adjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Primary Endpoint", "Column 8": "Trial phase", "Column 9": "Treatment regimen", "Column 10": "Control regimen"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting in relation to surgery": "Adjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting in relation to surgery": "Adjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting in relation to surgery": "Adjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting in relation to surgery": "Adjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Monotherapy/combination", "Column 9": "Type of combination", "Column 10": "Control regimen"}}</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting in relation to surgery": "Adjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Treatment regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting in relation to surgery": "Adjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Monotherapy/combination", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting in relation to surgery": "Adjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
     </row>
@@ -740,8 +680,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Class of ICI": "PD1, CTLA-4 or both",
-    "Cancer type": "Renal cell"
+    "ICI Class": "PD-1, CTLA-4 or both",
+    "Cancer Type": "Renal Cell Carcinoma (RCC)"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -759,27 +699,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "ICI Class": "PD1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Control regimen", "Column 7": "Type of Therapy"}}</t>
+          <t>{"selected_filter": {"ICI Class": "CTLA-4", "Cancer Type": "Renal Cell Carcinoma (RCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "ICI Class": "PD1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Type of combination", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"ICI Class": "CTLA-4", "Cancer Type": "Renal Cell Carcinoma (RCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"ICI Class": "CTLA-4", "Cancer Type": "Renal Cell Carcinoma (RCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Control regimen", "Column 7": "Class of ICI", "Column 8": "Primary Endpoint", "Column 9": "Monotherapy/combination", "Column 10": "Type of combination"}}</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "ICI Class": "PD1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Type of combination"}}</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "ICI Class": "PD1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Control regimen", "Column 7": "Name of ICI", "Column 8": "Class of ICI", "Column 9": "Monotherapy/combination", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"ICI Class": "CTLA-4", "Cancer Type": "Renal Cell Carcinoma (RCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -793,7 +723,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Class of ICI": "PD-L1"
+    "ICI Class": "PD-L1"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -808,27 +738,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Cancer type", "Column 7": "Type of Therapy", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Control regimen"}}</t>
+          <t>{"selected_filter": {"ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary endpoint"}}</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Cancer type", "Column 7": "Type of Therapy", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Control regimen"}}</t>
+          <t>{"selected_filter": {"ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Cancer type", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary endpoint"}}</t>
         </is>
       </c>
     </row>
@@ -858,27 +778,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Total sample size", "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 8": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 10": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos."}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Total sample size", "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 8": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Total sample size", "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 8": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 10": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details."}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Total sample size", "Column 7": "Cancer type", "Column 8": "Name of ICI", "Column 9": "Primary Endpoint", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Total sample size", "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 8": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Total sample size", "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 8": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 9": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."}}</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Total sample size", "Column 7": "Cancer type", "Column 8": "Name of ICI", "Column 9": "Monotherapy/combination", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Total sample size", "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 8": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
         </is>
       </c>
     </row>
@@ -892,7 +802,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Primary endpoint": "OS"
+    "Primary Endpoint": "OS"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -908,27 +818,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Cancer type –", "Column 7": "Name of ICI –", "Column 8": "Control regimen", "Column 9": "Type of combination –", "Column 10": "Total sample size –"}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Type of combination"}}</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 10": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos."}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 10": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos."}}</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Cancer type", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Type of combination"}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 10": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos."}}</t>
         </is>
       </c>
     </row>
@@ -957,27 +857,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 7": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 8": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Trial phase", "Column 9": "Primary endpoint", "Column 10": "Type of Study"}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Trial phase", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 8": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Trial phase", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -991,8 +881,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Class of ICI": "PD1",
-    "Monotherapy/combination": "Monotherapy"
+    "ICI Class": "PD-1",
+    "Type of Therapy": "Monotherapy"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -1009,27 +899,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"ICI Class": "PD1", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary endpoint", "Column 8": "Total sample size", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"ICI Class": "PD-1", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary endpoint", "Column 8": "Total sample size", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of Therapy": "Monotherapy", "ICI Class": "PD1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary endpoint", "Column 8": "Total sample size", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"ICI Class": "PD-1", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary endpoint", "Column 8": "Total sample size", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"ICI Class": "PD1", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary endpoint", "Column 8": "Total sample size", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"ICI Class": "PD1", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Primary endpoint", "Column 7": "Name of ICI", "Column 8": "Total sample size", "Column 9": "Lines of treatment", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"ICI Class": "PD1", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary endpoint", "Column 8": "Total sample size", "Column 9": "Trial phase", "Column 10": "Lines of treatment"}}</t>
+          <t>{"selected_filter": {"ICI Class": "PD-1", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary endpoint", "Column 8": "Total sample size", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
     </row>
@@ -1043,8 +923,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Class of ICI": "PD-L1",
-    "Monotherapy/combination": "Combination"
+    "ICI Class": "PD-L1",
+    "Type of Therapy": "Combination Therapy"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -1061,27 +941,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"ICI Class": "PD-L1", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Type of combination", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"ICI Class": "PD-L1", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"ICI Class": "PD-L1", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 8": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
+          <t>{"selected_filter": {"ICI Class": "PD-L1", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of Therapy": "Combination Therapy", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"ICI Class": "PD-L1", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"ICI Class": "PD-L1", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"ICI Class": "PD-L1", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -1095,8 +965,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Class of ICI": "CTLA4",
-    "Monotherapy/combination": "Monotherapy"
+    "ICI Class": "CTLA-4",
+    "Type of Therapy": "Monotherapy"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -1113,27 +983,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"ICI Class": "CTLA-4", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Type of Study"}}</t>
+          <t>{"selected_filter": {"ICI Class": "CTLA-4", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Trial phase", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"ICI Class": "CTLA-4", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Primary endpoint", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"ICI Class": "CTLA-4", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>{"selected_filter": {"ICI Class": "CTLA-4", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"ICI Class": "CTLA-4", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Type of Study"}}</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"ICI Class": "CTLA-4", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Clinical setting in relation to surgery", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -1147,8 +1007,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Class of ICI": "CTLA4",
-    "Monotherapy/combination": "Combination"
+    "ICI Class": "CTLA-4",
+    "Type of Therapy": "Combination Therapy"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -1165,25 +1025,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"ICI Class": "CTLA-4", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."}}</t>
+          <t>{"selected_filter": {"ICI Class": "CTLA-4", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Type of combination", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"ICI Class": "CTLA-4", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 7": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 8": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 10": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab)."}}</t>
+          <t>{"selected_filter": {"ICI Class": "CTLA-4", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Type of combination", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"ICI Class": "CTLA-4", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant", "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details", "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice)", "Column 9": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)", "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)"}}</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"ICI Class": "CTLA-4", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 9": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
         <is>
           <t>{"selected_filter": {"ICI Class": "CTLA-4", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."}}</t>
         </is>
@@ -1216,27 +1066,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "ICI Class": "PD1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Type of combination", "Column 8": "Clinical Setting in relation to surgery", "Column 9": "Control regimen", "Column 10": "Monotherapy/combination"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Treatment regimen", "Column 8": "Clinical Setting in Relation to Surgery", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Monotherapy/combination", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Primary Endpoint", "Column 8": "Monotherapy/combination", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1090,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Name of ICI": "Pembrolizumab",
+    "ICI Name": "Pembrolizumab",
     "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
     "Trial Phase": "Phase 3"
   },
@@ -1267,27 +1107,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3", "Name of ICI": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Lines of treatment"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3", "ICI Name": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Lines of treatment", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Name of ICI": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Lines of treatment", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3", "ICI Name": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Lines of treatment", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3", "Name of ICI": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Control regimen", "Column 7": "Monotherapy/combination", "Column 8": "Lines of treatment", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3", "Name of ICI": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Study name", "Column 7": "Total sample size", "Column 8": "Monotherapy/combination", "Column 9": "Control regimen", "Column 10": "Type of combination"}}</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3", "Name of ICI": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Total sample size", "Column 10": "Lines of treatment"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3", "ICI Name": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Lines of treatment", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1131,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Name of ICI": "Nivolumab",
+    "ICI Name": "Nivolumab",
     "Cancer Type": "Melanoma"
   },
   "selected_column": {
@@ -1319,27 +1149,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Name of ICI": "Nivolumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Monotherapy/combination", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Trial phase", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "ICI Name": "Nivolumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Monotherapy/combination", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "ICI Name": "Nivolumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "ICI Name": "Nivolumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Monotherapy/combination", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Name of ICI": "Nivolumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Monotherapy/combination", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Name of ICI": "Nivolumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Monotherapy/combination", "Column 6": "Type of combination", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Name of ICI": "Nivolumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "ICI Name": "Nivolumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Monotherapy/combination", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
     </row>
@@ -1354,8 +1174,8 @@
           <t>{
   "selected_filter": {
     "Cancer Type": "Breast",
-    "Name of ICI": "Atezolizumab",
-    "Type of combination": "ICI + Chemo",
+    "ICI Name": "Atezolizumab",
+    "Type of combination (Treatment Arm)": "ICI + Chemo",
     "Is PD-L1 positivity inclusion criteria": "Yes"
   },
   "selected_column": {
@@ -1373,27 +1193,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Breast", "ICI Name": "Atezolizumab", "Type of Therapy": "Combination Therapy", "Is PD-L1 positivity inclusion criteria": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Primary Endpoint", "Column 7": "Number of arms", "Column 8": "Class of ICI", "Column 9": "Cancer type", "Column 10": "Type of combination"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Breast", "Name of ICI": "Atezolizumab", "Type of Therapy": "Combination Therapy", "Is PD-L1 positivity inclusion criteria": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 9": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."}}</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Breast", "Name of ICI": "Atezolizumab", "Type of Therapy": "Combination Therapy", "Is PD-L1 positivity inclusion criteria": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 9": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Breast", "Name of ICI": "Atezolizumab", "Type of Therapy": "Combination Therapy", "Is PD-L1 positivity inclusion criteria": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Primary Endpoint", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Breast", "Name of ICI": "Atezolizumab", "Type of combination (Treatment Arm)": "ICI + Chemo", "Is PD-L1 positivity inclusion criteria": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 7": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 8": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 10": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice)."}}</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Breast", "Name of ICI": "Atezolizumab", "Is PD-L1 positivity inclusion criteria": "Yes", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Type of combination", "Column 10": "Monotherapy/combination"}}</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Breast", "ICI Name": "Atezolizumab", "Type of Therapy": "Combination Therapy", "Is PD-L1 positivity inclusion criteria": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Breast", "Name of ICI": "Atezolizumab", "Type of Therapy": "Combination Therapy", "Is PD-L1 positivity inclusion criteria": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 9": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."}}</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1217,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Name of ICI": "Avelumab",
+    "ICI Name": "Avelumab",
     "Cancer Type": "Bladder"
   },
   "selected_column": {
@@ -1425,27 +1235,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Bladder", "ICI Name": "Avelumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Clinical setting in relation to surgery", "Column 7": "Primary Endpoint", "Column 8": "Monotherapy/combination", "Column 9": "Treatment regimen", "Column 10": "Control regimen"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Bladder", "ICI Name": "Avelumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Clinical setting in relation to surgery", "Column 6": "Primary Endpoint", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Lines of treatment"}}</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Bladder", "ICI Name": "Avelumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Clinical setting in relation to surgery", "Column 6": "Type of Therapy", "Column 7": "Treatment regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Control regimen"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Bladder", "ICI Name": "Avelumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Clinical setting in relation to surgery", "Column 6": "Primary Endpoint", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Lines of treatment"}}</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Bladder", "ICI Name": "Avelumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Clinical setting in relation to surgery", "Column 6": "Primary Endpoint", "Column 7": "Treatment regimen", "Column 8": "Name of ICI", "Column 9": "Monotherapy/combination", "Column 10": "Control regimen"}}</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
           <t>{"selected_filter": {"Cancer Type": "Bladder", "ICI Name": "Avelumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Clinical setting in relation to surgery", "Column 6": "Primary Endpoint", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Lines of treatment"}}</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Bladder", "ICI Name": "Avelumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Clinical setting in relation to surgery", "Column 6": "Primary Endpoint", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Monotherapy/combination"}}</t>
         </is>
       </c>
     </row>
@@ -1459,8 +1259,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Name of ICI": "Tremelimumab",
-    "Cancer Type": "Hepatocellular carcinoma"
+    "ICI Name": "Tremelimumab",
+    "Cancer Type": "Hepatocellular carcinoma (HCC)"
   },
   "selected_column": {
     "Column 1": "Treatment regimen",
@@ -1477,27 +1277,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)", "Name of ICI": "Tremelimumab", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)", "ICI Name": "Tremelimumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Monotherapy/combination"}}</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)", "Name of ICI": "Tremelimumab", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Primary Endpoint", "Column 8": "Control regimen", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)", "ICI Name": "Tremelimumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Monotherapy/combination"}}</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Trial phase", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)", "ICI Name": "Tremelimumab", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Primary Endpoint", "Column 8": "Control regimen", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)", "ICI Name": "Tremelimumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Monotherapy/combination"}}</t>
         </is>
       </c>
     </row>
@@ -1511,10 +1301,10 @@
         <is>
           <t>{
   "selected_filter": {
-    "Name of ICI": "Durvalumab",
-    "Cancer Type": "NSCLC",
+    "ICI Name": "Durvalumab",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
     "Clinical Setting": "Maintenance",
-    "Type of control": "Placebo"
+    "Control Arm": "Placebo"
   },
   "selected_column": {
     "Column 1": "Study name",
@@ -1531,27 +1321,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Clinical Setting": "Maintenance", "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting": "Maintenance"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Trial phase", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting": "Maintenance"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Total sample size", "Column 9": "Name of ICI", "Column 10": "Monotherapy/combination"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting": "Maintenance"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Trial phase", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Clinical Setting": "Maintenance", "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Trial phase", "Column 7": "Primary Endpoint", "Column 8": "Type of Therapy", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Clinical Setting": "Maintenance", "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting": "Maintenance"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting": "Maintenance"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Trial phase", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
     </row>
@@ -1566,9 +1346,9 @@
           <t>{
   "selected_filter": {
     "Trial Phase": "Phase 3",
-    "Class of ICI": "PD1",
-    "Cancer Type": "NSCLC",
-    "Monotherapy/combination": "Combination"
+    "ICI Class": "PD-1",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of Therapy": "Combination Therapy"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -1585,27 +1365,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3", "ICI Class": "PD1", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Total sample size", "Column 6": "Primary Endpoint", "Column 7": "Name of ICI", "Column 8": "Treatment regimen", "Column 9": "Monotherapy/combination", "Column 10": "Control regimen"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3", "ICI Class": "PD-1", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Total sample size", "Column 6": "Primary endpoint", "Column 7": "Name of ICI", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Type of combination"}}</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3", "Type of Therapy": "Combination Therapy", "ICI Class": "PD1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Total sample size", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Primary endpoint", "Column 9": "Control regimen", "Column 10": "Type of combination"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3", "ICI Class": "PD-1", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Total sample size", "Column 6": "Primary endpoint", "Column 7": "Name of ICI", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Type of combination"}}</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3", "Class of ICI": "PD1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Total sample size", "Column 7": "Name of ICI", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Type of combination"}}</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Class of ICI": "PD-1 inhibitor", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Total sample size", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Type of combination", "Column 10": "Lines of treatment"}}</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3", "ICI Class": "PD1", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Total sample size", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Lines of treatment"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3", "ICI Class": "PD-1", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Total sample size", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Lines of treatment"}}</t>
         </is>
       </c>
     </row>
@@ -1619,8 +1389,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Class of ICI": "PD-L1",
-    "Monotherapy/combination": "Monotherapy"
+    "ICI Class": "PD-L1",
+    "Type of Therapy": "Monotherapy"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -1637,27 +1407,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"ICI Class": "PD-L1", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Lines of treatment", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"ICI Class": "PD-L1", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Lines of treatment"}}</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of Therapy": "Monotherapy", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Lines of treatment", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"ICI Class": "PD-L1", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Lines of treatment"}}</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of Therapy": "Monotherapy", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Lines of treatment"}}</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of Therapy": "Monotherapy", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Clinical setting in relation to surgery", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Lines of treatment"}}</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"ICI Class": "PD-L1", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"ICI Class": "PD-L1", "Type of Therapy": "Monotherapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Lines of treatment"}}</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1431,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of combination": "ICI + ICI"
+    "Type of combination (Treatment Arm)": "ICI + ICI"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -1688,27 +1448,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Clinical setting in relation to surgery", "Column 8": "Primary endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Trial phase", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Primary Endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."}}</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Clinical setting in relation to surgery", "Column 8": "Primary endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Trial phase", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
     </row>
@@ -1722,8 +1472,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "NSCLC",
-    "Type of combination": "ICI + Chemo"
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of combination (Treatment Arm)": "ICI + Chemo"
   },
   "selected_column": {
     "Column 1": "Study name",
@@ -1740,27 +1490,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Total sample size", "Column 9": "Trial phase", "Column 10": "Lines of treatment"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of Therapy": "Combination Therapy", "Type of combination (Treatment Arm)": "ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Lines of treatment", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Total sample size", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of Therapy": "Combination Therapy", "Type of combination (Treatment Arm)": "ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Lines of treatment", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Total sample size", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Study name", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of Therapy": "Combination Therapy", "Type of combination (Treatment Arm)": "ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Lines of treatment", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1514,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of combination": "ICI + TKI"
+    "Type of combination (Treatment Arm)": "ICI + TKI"
   },
   "selected_column": {
     "Column 1": "Treatment regimen",
@@ -1791,27 +1531,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Clinical setting in relation to surgery", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1555,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of combination": "ICI + Radiation"
+    "Type of combination (Treatment Arm)": "ICI + Radiation"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -1842,27 +1572,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + RadiatICln (Radiation/Clinical Radiation)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + RadiatICln (Radiation/Clinical Radiation)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + RadiatICln (Radiation/Clinical Radiation)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + RadiatICln (Radiation/Clinical Radiation)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + RadiatICln (Radiation/Clinical Radiation)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary endpoint", "Column 8": "Control regimen", "Column 9": "Total sample size", "Column 10": "Monotherapy/combination"}}</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + RadiatICln (Radiation/Clinical Radiation)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + RadiatICln (Radiation/Clinical Radiation)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Treatment regimen"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + RadiatICln (Radiation/Clinical Radiation)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1596,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of combination": "ICI + Vaccine"
+    "Type of combination (Treatment Arm)": "ICI + Vaccine"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -1893,7 +1613,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Vaccine"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary endpoint", "Column 8": "Total sample size", "Column 9": "Treatment regimen", "Column 10": "Control regimen"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Vaccine"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1903,17 +1623,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Vaccine"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Vaccine"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Cancer type", "Column 7": "Treatment regimen", "Column 8": "Name of ICI", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Vaccine"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Vaccine"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1637,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of combination": "ICI + BRAFi + MEKi",
+    "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi",
     "Cancer Type": "Melanoma"
   },
   "selected_column": {
@@ -1945,25 +1655,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Name of ICI", "Column 8": "Type of combination", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Name of ICI", "Column 8": "Treatment regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Treatment regimen", "Column 8": "Monotherapy/combination", "Column 9": "Primary Endpoint", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Name of ICI", "Column 8": "Treatment regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Primary Endpoint", "Column 8": "Name of ICI", "Column 9": "Treatment regimen", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
         <is>
           <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Name of ICI", "Column 8": "Treatment regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
@@ -1979,7 +1679,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of combination": "ICI + Anti-VEGF"
+    "Type of combination (Treatment Arm)": "ICI + Anti-VEGF"
   },
   "selected_column": {
     "Column 1": "Treatment regimen",
@@ -1996,7 +1696,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 10": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial."}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2005,16 +1705,6 @@
         </is>
       </c>
       <c r="E31" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
         <is>
           <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
         </is>
@@ -2030,7 +1720,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of combination": "ICI + Chemo + Anti-VEGF"
+    "Type of combination (Treatment Arm)": "ICI + Chemo + Anti-VEGF"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -2047,27 +1737,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Chemo + Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Lines of treatment"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Chemo + Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Chemo + Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Chemo + Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Chemo + Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Monotherapy/combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Chemo + Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Chemo + Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + Chemo + Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -2081,7 +1761,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of combination": "ICI + ICI + Chemo"
+    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -2098,27 +1778,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Primary Endpoint", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary endpoint"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -2133,7 +1803,7 @@
           <t>{
   "selected_filter": {
     "Trial Phase": "Phase 3",
-    "Type of control": "Placebo"
+    "Control Arm": "Placebo"
   },
   "selected_column": {
     "Column 1": "Study name",
@@ -2150,27 +1820,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Type of Control": "Placebo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab)", "Column 7": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)", "Column 8": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms", "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination)", "Column 10": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details"}}</t>
+          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Type of control": "Placebo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Type of Therapy", "Column 8": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 9": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms.", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Type of control": "Placebo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 8": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
+          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Type of control": "Placebo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Type of Therapy", "Column 8": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 9": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms.", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Type of Control": "Placebo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Type of control": "Placebo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Type of control": "Placebo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary endpoint", "Column 8": "Total sample size", "Column 9": "Control regimen", "Column 10": "Type of combination"}}</t>
+          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Type of Control": "Placebo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary endpoint", "Column 8": "Total sample size", "Column 9": "Monotherapy/combination", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
     </row>
@@ -2184,8 +1844,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "NSCLC",
-    "Type of control": "Chemo"
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Control Arm": "Chemo"
   },
   "selected_column": {
     "Column 1": "Study name",
@@ -2202,27 +1862,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Control Arm": "Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Clinical setting in relation to surgery", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Control Arm": "Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Clinical Setting in relation to surgery", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Control Arm": "Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Total sample size", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Control Arm": "Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Clinical Setting in relation to surgery", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Control Arm": "Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Type of combination"}}</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Control Arm": "Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Clinical setting in relation to surgery", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Control Arm": "Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Trial phase", "Column 7": "Type of combination", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Monotherapy/combination"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Control Arm": "Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Name of ICI", "Column 8": "Type of combination", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -2236,8 +1886,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "Hepatocellular carcinoma",
-    "Type of control": "TKI"
+    "Cancer Type": "Hepatocellular carcinoma (HCC)",
+    "Control Arm": "TKI"
   },
   "selected_column": {
     "Column 1": "Control regimen",
@@ -2254,27 +1904,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)", "Type of Control": "Active-controlled (specific drug/therapy)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Control regimen", "Column 7": "Clinical Setting in relation to surgery", "Column 8": "Monotherapy/combination", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)", "Type of Control": "TKI (Tyrosine Kinase Inhibitor)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)", "Type of Control": "TKI (Tyrosine Kinase Inhibitor)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)", "Type of Control": "TKI (Tyrosine Kinase Inhibitor)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)", "Type of Control": "Active-controlled (specific drug/therapy)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Monotherapy/combination"}}</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)", "Type of control": "active-controlled (specific drug/therapy)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)", "Type of control": "active-controlled (specific drug/therapy)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Trial phase", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)", "Type of Control": "TKI (Tyrosine Kinase Inhibitor)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -2288,7 +1928,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of control": "Interferon"
+    "Control Arm": "Interferon"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -2305,27 +1945,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Interferon"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Interferon"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Interferon"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Interferon"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Interferon"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary endpoint", "Column 9": "Monotherapy/combination", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Control Arm": "Interferon"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Control Arm": "Interferon"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Interferon"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
     </row>
@@ -2339,7 +1969,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of control": "Best Supportive Care"
+    "Control Arm": "Best Supportive Care"
   },
   "selected_column": {
     "Column 1": "Study name",
@@ -2356,27 +1986,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Best Supportive Care (BSC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Clinical setting in relation to surgery", "Column 8": "Primary endpoint", "Column 9": "Monotherapy/combination", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Best Supportive Care (BSC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Best Supportive Care (BSC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Monotherapy/combination", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary endpoint"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Best Supportive Care (BSC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Best Supportive Care (BSC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Primary endpoint"}}</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Control Arm": "Best Supportive Care (BSC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Primary Endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 8": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 9": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Control Arm": "Best Supportive Care (BSC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Trial phase", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Type of Study"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Best Supportive Care (BSC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2010,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of control": "Chemo / Anti-EGFR"
+    "Control Arm": "Chemo / Anti-EGFR"
   },
   "selected_column": {
     "Column 1": "Control regimen",
@@ -2407,27 +2027,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Chemo / Anti-EGFR"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Type of combination", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Chemo / Anti-EGFR"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Chemo / Anti-EGFR"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Chemo / Anti-EGFR"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Chemo / Anti-EGFR"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Primary Endpoint", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Control Arm": "Chemo / Anti-EGFR"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Control Arm": "Chemo / Anti-EGFR"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Chemo / Anti-EGFR"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2051,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of control": "Chemo / Anti-VEGF"
+    "Control Arm": "Chemo / Anti-VEGF"
   },
   "selected_column": {
     "Column 1": "Control regimen",
@@ -2458,27 +2068,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Chemo / Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Chemo / Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Chemo / Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Monotherapy/combination"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Chemo / Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Chemo / Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Control Arm": "Chemo / Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Clinical setting in relation to surgery", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Control Arm": "Chemo / Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Chemo / Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2092,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of control": "mTOR inhibitor"
+    "Control Arm": "mTOR inhibitor"
   },
   "selected_column": {
     "Column 1": "Control regimen",
@@ -2509,27 +2109,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "mTOR inhibitor"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Name of ICI"}}</t>
+          <t>{"selected_filter": {"Control Arm": "mTOR inhibitor"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "mTOR inhibitor"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary endpoint", "Column 9": "Trial phase", "Column 10": "Type of combination"}}</t>
+          <t>{"selected_filter": {"Control Arm": "mTOR inhibitor"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "mTOR inhibitor"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Control regimen", "Column 7": "Type of control", "Column 8": "Treatment regimen", "Column 9": "Name of ICI", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Control Arm": "mTOR inhibitor"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Clinical setting in relation to surgery", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Control Arm": "mTOR inhibitor"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary endpoint", "Column 9": "Type of Study", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Control Arm": "mTOR inhibitor"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2133,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of control": "Multikinase inhibitor"
+    "Control Arm": "Multikinase inhibitor"
   },
   "selected_column": {
     "Column 1": "Control regimen",
@@ -2560,25 +2150,15 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Multikinase inhibitor"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Multikinase inhibitor"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Multikinase inhibitor"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Multikinase inhibitor"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Control Arm": "Multikinase inhibitor"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Trial phase", "Column 10": "Type of Study"}}</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Control Arm": "Multikinase inhibitor"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
         <is>
           <t>{"selected_filter": {"Control Arm": "Multikinase inhibitor"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
@@ -2594,7 +2174,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of control": "Vaccine"
+    "Control Arm": "Vaccine"
   },
   "selected_column": {
     "Column 1": "Control regimen",
@@ -2611,27 +2191,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Vaccine"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Vaccine"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Vaccine"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Type of combination", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Vaccine"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Vaccine"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 8": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 9": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial.", "Column 10": "Type of Study"}}</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Control Arm": "Vaccine"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 8": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 9": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial.", "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."}}</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Control Arm": "Vaccine"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
+          <t>{"selected_filter": {"Control Arm": "Vaccine"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2215,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of control": "Radiation"
+    "Control Arm": "Radiation"
   },
   "selected_column": {
     "Column 1": "Control regimen",
@@ -2662,27 +2232,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Radiation"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Radiation"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Radiation"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Clinical setting in relation to surgery", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Radiation"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Control Arm": "Radiation"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Control Arm": "Radiation"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Trial phase", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Type of Therapy", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Control Arm": "Radiation"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Clinical setting in relation to surgery", "Column 9": "Primary endpoint", "Column 10": "Type of Study"}}</t>
+          <t>{"selected_filter": {"Control Arm": "Radiation"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -2714,27 +2274,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Clinical Setting": "Adjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Clinical Setting": "Adjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Treatment regimen", "Column 10": "Control regimen"}}</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Clinical Setting": "Adjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Trial phase", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Clinical Setting": "Adjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Treatment regimen", "Column 10": "Control regimen"}}</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Clinical Setting": "Adjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Clinical Setting": "Adjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Treatment regimen"}}</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Clinical Setting": "Adjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Clinical Setting": "Adjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Treatment regimen", "Column 10": "Control regimen"}}</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2298,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "NSCLC",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
     "Clinical Setting": "Neoadjuvant"
   },
   "selected_column": {
@@ -2766,27 +2316,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting in relation to surgery": "Neoadjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting in relation to surgery": "Neoadjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting in relation to surgery": "Neoadjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting in relation to surgery": "Neoadjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary endpoint", "Column 6": "Study name", "Column 7": "Name of ICI", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting": "Neoadjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting in relation to surgery": "Neoadjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting in relation to surgery": "Neoadjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting in relation to surgery": "Neoadjuvant"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2340,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Primary endpoint": "Path CR"
+    "Primary Endpoint": "Path CR"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -2817,27 +2357,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "Path CR (Pathologic Complete Response; pCR)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Trial phase", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 9": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 10": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details."}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "Path CR (Pathologic Complete Response; pCR)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 10": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial."}}</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "Path CR (Pathologic Complete Response; pCR)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial.", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "Path CR (Pathologic Complete Response; pCR)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 10": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial."}}</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "Path CR (Pathologic Complete Response; pCR)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 8": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 9": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 10": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice)."}}</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "Path CR (Pathologic Complete Response; pCR)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 8": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 9": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial.", "Column 10": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details."}}</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "Path CR (Pathologic Complete Response; pCR)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Trial phase", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 9": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "Path CR (Pathologic Complete Response; pCR)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 10": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial."}}</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2381,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Primary endpoint": "ORR"
+    "Primary Endpoint": "ORR"
   },
   "selected_column": {
     "Column 1": "Trial phase",
@@ -2868,27 +2398,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "ORR (Objective Response Rate)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Trial phase", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 9": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "ORR (Objective Response Rate)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial.", "Column 8": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 9": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "ORR (Objective Response Rate)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Trial phase", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 9": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "ORR (Objective Response Rate)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial.", "Column 8": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 9": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "ORR (Objective Response Rate)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "ORR (Objective Response Rate)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "ORR (Objective Response Rate)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Cancer type", "Column 7": "Trial phase", "Column 8": "Monotherapy/combination", "Column 9": "Type of combination", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "ORR (Objective Response Rate)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial.", "Column 8": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 9": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2422,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Primary endpoint": "OS"
+    "Primary Endpoint": "OS"
   },
   "selected_column": {
     "Column 1": "Trial phase",
@@ -2919,27 +2439,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 8": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 9": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 10": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial."}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Trial phase", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 8": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial.", "Column 9": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 7": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 8": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 9": "Trial phase", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2463,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Primary endpoint": "PFS"
+    "Primary Endpoint": "PFS"
   },
   "selected_column": {
     "Column 1": "Trial phase",
@@ -2970,27 +2480,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "PFS (Progression-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "PFS (Progression-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "PFS (Progression-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "PFS (Progression-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "PFS (Progression-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "PFS (Progression-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "PFS (Progression-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "PFS (Progression-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
     </row>
@@ -3004,7 +2504,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Primary endpoint": "RFS"
+    "Primary Endpoint": "RFS"
   },
   "selected_column": {
     "Column 1": "Clinical setting in relation to surgery",
@@ -3021,27 +2521,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "RFS (Recurrence-/Relapse-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial.", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "RFS (Recurrence-/Relapse-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "RFS (Recurrence-/Relapse-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms.", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "RFS (Recurrence-/Relapse-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "RFS (Recurrence-/Relapse-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Monotherapy/combination"}}</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "RFS (Recurrence-/Relapse-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "RFS (Recurrence-/Relapse-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 8": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms.", "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 10": "Lines of treatment – How many prior systemic therapy “lines” a patient has received for the disease setting being studied (e.g., 1L = first-line, 2L = after one prior line); also used to specify the line under investigation."}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "RFS (Recurrence-/Relapse-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -3055,7 +2545,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Primary endpoint": "EFS"
+    "Primary Endpoint": "EFS"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -3072,27 +2562,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "EFS (Event-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary multiple, composite, or co-primary endpoints?"}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "EFS (Event-Free Survival) (in combos like Path CR+EFS)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "EFS (Event-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Cancer type", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "EFS (Event-Free Survival) (in combos like Path CR+EFS)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "EFS (Event-Free Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Clinical setting in relation to surgery", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "EFS (Event-Free Survival) (in combos like Path CR+EFS)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 8": "Trial phase", "Column 9": "Primary endpoint", "Column 10": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details."}}</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "EFS (Event-Free Survival) (in combos like Path CR+EFS)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 8": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 9": "Trial phase - The stage or step in the clinical trial process, typically denoted by a Roman numeral (e.g. I, II, III, IV), which defines the scope, objectives, and duration of the trial.", "Column 10": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos."}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "EFS (Event-Free Survival) (in combos like Path CR+EFS)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary endpoint"}}</t>
         </is>
       </c>
     </row>
@@ -3106,7 +2586,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Primary endpoint": "Safety"
+    "Primary Endpoint": "Safety"
   },
   "selected_column": {
     "Column 1": "Treatment regimen",
@@ -3123,27 +2603,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "Safety"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Cancer type", "Column 7": "Trial phase", "Column 8": "Name of ICI", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "Safety"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "Safety"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "Safety"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Primary endpoint"}}</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "Safety"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Cancer type", "Column 7": "Treatment regimen", "Column 8": "Name of ICI", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "Safety"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "Safety"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "Safety"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
         </is>
       </c>
     </row>
@@ -3157,7 +2627,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "NSCLC",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
     "Is PD-L1 positivity inclusion criteria": "Yes"
   },
   "selected_column": {
@@ -3175,27 +2645,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Is PD-L1 positivity inclusion criteria": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Is PD-L1 positivity inclusion criteria": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Is PD-L1 positivity inclusion criteria": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Clinical setting in relation to surgery", "Column 8": "Trial phase", "Column 9": "Type of combination", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Is PD-L1 positivity inclusion criteria": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Is PD-L1 positivity inclusion criteria": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Primary Endpoint", "Column 8": "Trial phase", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Is PD-L1 positivity inclusion criteria": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Clinical setting in relation to surgery", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Is PD-L1 positivity inclusion criteria": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Is PD-L1 positivity inclusion criteria": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
     </row>
@@ -3227,27 +2687,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Colorectal", "Is any other biomarker used for inclusion": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Treatment regimen"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Colorectal", "Is any other biomarker used for inclusion": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Colorectal", "Is any other biomarker used for inclusion": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Primary Endpoint", "Column 8": "Total sample size", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Treatment regimen"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Colorectal", "Is any other biomarker used for inclusion": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Colorectal", "Is any other biomarker used for inclusion": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Primary Endpoint", "Column 8": "Control regimen", "Column 9": "Total sample size", "Column 10": "Type of combination"}}</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Colorectal", "Is any other biomarker used for inclusion": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Primary Endpoint", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Colorectal", "Is any other biomarker used for inclusion": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Primary Endpoint", "Column 10": "Control regimen"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Colorectal", "Is any other biomarker used for inclusion": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -3279,27 +2729,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Pancreatic Cancer", "Is any other biomarker used for inclusion": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Is any other biomarker used for inclusion"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Pancreatic Cancer", "Is any other biomarker used for inclusion": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Is any other biomarker used for inclusion", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Pancreatic Cancer", "Is any other biomarker used for inclusion": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Is any other biomarker used for inclusion"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Pancreatic Cancer", "Is any other biomarker used for inclusion": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Is any other biomarker used for inclusion", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>{"selected_filter": {"Cancer Type": "Pancreatic Cancer", "Is any other biomarker used for inclusion": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Is any other biomarker used for inclusion", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Pancreatic Cancer", "Is any other biomarker used for inclusion": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Is any other biomarker used for inclusion", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Pancreatic Cancer", "Is any other biomarker used for inclusion": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Is any other biomarker used for inclusion", "Column 9": "Clinical Setting in relation to surgery", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
     </row>
@@ -3331,27 +2771,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Prostate"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Is any other biomarker used for inclusion", "Column 7": "Name of ICI", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Prostate"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Is any other biomarker used for inclusion", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Prostate"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Primary Endpoint", "Column 10": "Is any other biomarker used for inclusion"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Prostate"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Is any other biomarker used for inclusion", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Prostate"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Is any other biomarker used for inclusion", "Column 8": "Monotherapy/combination", "Column 9": "Treatment regimen", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Prostate"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Is any other biomarker used for inclusion", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Primary Endpoint", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Prostate"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Is any other biomarker used for inclusion", "Column 7": "Monotherapy/combination", "Column 8": "Primary Endpoint", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Prostate"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Is any other biomarker used for inclusion", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
     </row>
@@ -3382,25 +2812,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Multiple Myeloma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Multiple Myeloma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Study name", "Column 7": "Name of ICI", "Column 8": "Monotherapy/combination", "Column 9": "Treatment regimen", "Column 10": "Control regimen"}}</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Multiple Myeloma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Multiple Myeloma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Study name", "Column 7": "Name of ICI", "Column 8": "Monotherapy/combination", "Column 9": "Treatment regimen", "Column 10": "Control regimen"}}</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Multiple Myeloma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Study name", "Column 7": "Name of ICI", "Column 8": "Monotherapy/combination", "Column 9": "Treatment regimen", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Multiple Myeloma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI"}}</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
         <is>
           <t>{"selected_filter": {"Cancer Type": "Multiple Myeloma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI"}}</t>
         </is>
@@ -3433,27 +2853,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Mesothelioma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Mesothelioma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Mesothelioma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Primary Endpoint", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Mesothelioma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Mesothelioma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Name of ICI", "Column 7": "Class of ICI", "Column 8": "Monotherapy/combination", "Column 9": "Type of combination", "Column 10": "Control regimen"}}</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Mesothelioma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Type of combination", "Column 9": "Monotherapy/combination", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Mesothelioma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Control regimen", "Column 7": "Name of ICI", "Column 8": "Monotherapy/combination", "Column 9": "Type of combination", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Mesothelioma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Treatment regimen", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
     </row>
@@ -3467,7 +2877,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "NSCLC",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
     "Type of Study": "Follow-up"
   },
   "selected_column": {
@@ -3484,27 +2894,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of Study": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Treatment regimen", "Column 8": "Name of ICI", "Column 9": "Monotherapy/combination", "Column 10": "Primary endpoint"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Original/Follow Up": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Name of ICI", "Column 8": "Monotherapy/combination", "Column 9": "Primary endpoint", "Column 10": "Follow-up duration for primary endpoint(s) in months"}}</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of Study": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Primary endpoint", "Column 8": "Follow-up duration for primary endpoint(s) in months", "Column 9": "Name of ICI", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of Study": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Name of ICI", "Column 8": "Primary endpoint", "Column 9": "Follow-up duration for primary endpoint(s) in months", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of Study": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Name of ICI", "Column 8": "Primary endpoint", "Column 9": "Follow-up duration for primary endpoint(s) in months [Overall]", "Column 10": "Type of follow-up given"}}</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of Study": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Name of ICI", "Column 8": "Primary endpoint", "Column 9": "Follow-up duration for primary endpoint(s) in months", "Column 10": "Type of follow-up given"}}</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of Study": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Name of ICI", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Type of follow-up given"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Original/Follow Up": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Name of ICI", "Column 8": "Monotherapy/combination", "Column 9": "Primary endpoint", "Column 10": "Follow-up duration for primary endpoint(s) in months"}}</t>
         </is>
       </c>
     </row>
@@ -3535,27 +2935,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Study": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Original/Follow Up", "Column 6": "Study name", "Column 7": "Name of ICI", "Column 8": "Type of combination", "Column 9": "Primary Endpoint", "Column 10": "Follow-up duration for primary endpoint(s) in months"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Study": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Primary endpoint", "Column 9": "Follow-up duration for primary endpoint(s) in months", "Column 10": "Type of follow-up given"}}</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Study": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Clinical setting in relation to surgery", "Column 8": "Treatment regimen", "Column 9": "Primary Endpoint", "Column 10": "Follow-up duration for primary endpoint(s) in months"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Study": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Primary endpoint", "Column 9": "Follow-up duration for primary endpoint(s) in months", "Column 10": "Type of follow-up given"}}</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Study": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Original/Follow Up", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Primary Endpoint", "Column 9": "Follow-up duration for primary endpoint(s) in months", "Column 10": "Treatment regimen"}}</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Study": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Primary endpoint", "Column 9": "Follow-up duration for primary endpoint(s) in months", "Column 10": "Original publication or Follow-up"}}</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Study": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Original/Follow Up", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Primary Endpoint", "Column 9": "Follow-up duration for primary endpoint(s) in months [Overall]", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Study": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Primary endpoint", "Column 9": "Follow-up duration for primary endpoint(s) in months", "Column 10": "Type of follow-up given"}}</t>
         </is>
       </c>
     </row>
@@ -3588,27 +2978,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Primary multiple, composite, or co-primary endpoints?": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 9": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
+          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Primary multiple, composite, or co-primary endpoints?": "Co-primary endpoints"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Primary multiple, composite, or co-primary endpoints?": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Primary endpoint", "Column 7": "Primary multiple, composite, or co-primary endpoints?", "Column 8": "Name of ICI", "Column 9": "Treatment regimen", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Primary multiple, composite, or co-primary endpoints?": "Co-primary endpoints"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Primary multiple, composite, or co-primary endpoints?": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Primary endpoint", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Total sample size", "Column 10": "Treatment regimen"}}</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Primary multiple, composite, or co-primary endpoints?": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 7": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 8": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 9": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms.", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Primary multiple, composite, or co-primary endpoints?": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Cancer type", "Column 7": "Treatment regimen", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Trial Phase": "Phase 3", "Primary multiple, composite, or co-primary endpoints?": "Co-primary endpoints"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3002,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Primary endpoint": "OS"
+    "Primary Endpoint": "OS"
   },
   "selected_column": {
     "Column 1": "Follow-up duration for primary endpoint(s) in months",
@@ -3638,27 +3018,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months [Overall]", "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 7": "Trial phase", "Column 8": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 10": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos."}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Follow-up duration for primary endpoint(s) in months – The amount of follow-up available at the time of the primary analysis, reported in months:\n\t[Overall] – Median follow-up across the entire study population.", "Column 10": "Follow-up duration for primary endpoint(s) in months – The amount of follow-up available at the time of the primary analysis, reported in months:\n\t[Rx] – Median follow-up among participants in the treatment/experimental arm."}}</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Monotherapy/combination"}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Follow-up duration for primary endpoint(s) in months – The amount of follow-up available at the time of the primary analysis, reported in months:\n\t[Overall] – Median follow-up across the entire study population.", "Column 10": "Follow-up duration for primary endpoint(s) in months – The amount of follow-up available at the time of the primary analysis, reported in months:\n\t[Rx] – Median follow-up among participants in the treatment/experimental arm."}}</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months [Overall]", "Column 6": "Follow-up duration for primary endpoint(s) in months [Rx]", "Column 7": "Follow-up duration for primary endpoint(s) in months [Control]", "Column 8": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 9": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months [Overall]", "Column 6": "Follow-up duration for primary endpoint(s) in months [Rx]", "Column 7": "Follow-up duration for primary endpoint(s) in months [Control]", "Column 8": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant", "Column 9": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab)", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months [Overall]", "Column 6": "Follow-up duration for primary endpoint(s) in months [Rx]", "Column 7": "Follow-up duration for primary endpoint(s) in months [Control]", "Column 8": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant", "Column 9": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab)", "Column 10": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos"}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Follow-up duration for primary endpoint(s) in months – The amount of follow-up available at the time of the primary analysis, reported in months:\n\t[Overall] – Median follow-up across the entire study population.", "Column 10": "Follow-up duration for primary endpoint(s) in months – The amount of follow-up available at the time of the primary analysis, reported in months:\n\t[Rx] – Median follow-up among participants in the treatment/experimental arm."}}</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3042,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Primary endpoint": "PFS"
+    "Primary Endpoint": "PFS"
   },
   "selected_column": {
     "Column 1": "Follow-up duration for primary endpoint(s) in months",
@@ -3688,27 +3058,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "PFS"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Follow-up duration for primary endpoint(s) in months [Overall]", "Column 8": "Follow-up duration for primary endpoint(s) in months [Rx]", "Column 9": "Follow-up duration for primary endpoint(s) in months [Control]", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "PFS"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Follow-up duration for primary endpoint(s) in months", "Column 7": "Cancer type", "Column 8": "Name of ICI", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "PFS"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Follow-up duration for primary endpoint(s) in months [Overall]", "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 8": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "PFS"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Follow-up duration for primary endpoint(s) in months", "Column 7": "Cancer type", "Column 8": "Name of ICI", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Primary Endpoint": "PFS"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Follow-up duration for primary endpoint(s) in months"}}</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "PFS"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms.", "Column 8": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 9": "Follow-up duration for primary endpoint(s) in months – The amount of follow-up available at the time of the primary analysis, reported in months:\n\t[Overall] – Median follow-up across the entire study population.", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Primary Endpoint": "PFS"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Follow-up duration for primary endpoint(s) in months [Overall]", "Column 7": "Follow-up duration for primary endpoint(s) in months [Rx]", "Column 8": "Follow-up duration for primary endpoint(s) in months [Control]", "Column 9": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 10": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details."}}</t>
+          <t>{"selected_filter": {"Primary Endpoint": "PFS"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Follow-up duration for primary endpoint(s) in months", "Column 7": "Cancer type", "Column 8": "Name of ICI", "Column 9": "Treatment regimen", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -3737,27 +3097,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Number of arms", "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms.", "Column 10": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab)."}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Number of arms", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary endpoint"}}</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Number of arms", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Trial Phase": "Phase 2"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Number of arms", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Number of arms", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Number of arms", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Number of arms", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Monotherapy/combination", "Column 9": "Type of combination", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Trial Phase": "Phase 2"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Number of arms", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3121,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "NSCLC",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
     "Lines of treatment": "1L"
   },
   "selected_column": {
@@ -3789,27 +3139,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting": "Metastatic / Recurrent (Unresectable)", "Lines of treatment": "1L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Type of combination", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting": "Metastatic / Recurrent (Unresectable)", "Lines of treatment": "1L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting": "Metastatic / Recurrent (Unresectable)", "Lines of treatment": "Lines of treatment"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary endpoint", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Type of combination", "Column 9": "Monotherapy/combination", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting": "Metastatic / Recurrent (Unresectable)", "Lines of treatment": "Lines of treatment"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting": "Metastatic / Recurrent (Unresectable)", "Lines of treatment": "1L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting": "Metastatic / Recurrent (Unresectable)", "Lines of treatment": "Lines of treatment"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary endpoint", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting": "Metastatic / Recurrent (Unresectable)", "Lines of treatment": "1L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting": "Metastatic / Recurrent (Unresectable)", "Lines of treatment": "Lines of treatment"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
     </row>
@@ -3841,27 +3181,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Bladder", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Bladder", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Bladder", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Treatment regimen", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Bladder", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>{"selected_filter": {"Cancer Type": "Bladder", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Bladder", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Type of combination", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Bladder", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
     </row>
@@ -3875,7 +3205,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "Head and Neck",
+    "Cancer Type": "Head and Neck (HNSCC)",
     "Year": "2023+"
   },
   "selected_column": {
@@ -3892,27 +3222,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
     </row>
@@ -3926,8 +3246,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "NSCLC",
-    "Name of ICI": "Pembrolizumab",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "ICI Name": "Pembrolizumab",
     "Is PD-L1 positivity inclusion criteria": "Yes",
     "Trial Phase": "Phase 3"
   },
@@ -3944,27 +3264,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "ICI Name": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Primary endpoint", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Lines of treatment"}}</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Primary endpoint", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Primary endpoint", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Lines of treatment"}}</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Name of ICI": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Primary Endpoint", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Total sample size", "Column 10": "Lines of treatment"}}</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Primary endpoint", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Trial Phase": "Phase 3"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Primary endpoint", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Lines of treatment"}}</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3289,7 @@
           <t>{
   "selected_filter": {
     "Cancer Type": "Melanoma",
-    "Type of combination": "ICI + ICI",
+    "Type of combination (Treatment Arm)": "ICI + ICI",
     "Trial Phase": "Phase 3"
   },
   "selected_column": {
@@ -3995,27 +3305,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "ICI Name": "Nivolumab", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "ICI Name": "Nivolumab", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Cancer type", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Primary Endpoint", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Therapy": "Combination Therapy", "ICI Name": "Nivolumab", "Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Primary Endpoint", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -4045,27 +3345,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Secondary endpoint", "Column 6": "Study name", "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 8": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 9": "Type of Study", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Secondary endpoint", "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 9": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."}}</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Secondary endpoint", "Column 6": "Study name", "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 8": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Secondary endpoint", "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 9": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."}}</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Secondary endpoint", "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Trial phase", "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."}}</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Secondary endpoint", "Column 6": "Study name", "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 8": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 9": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 10": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice)."}}</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Secondary endpoint", "Column 6": "Name of ICI", "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 8": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Secondary endpoint", "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 9": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."}}</t>
         </is>
       </c>
     </row>
@@ -4094,7 +3384,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Original/Follow Up", "Column 6": "Type of follow-up given", "Column 7": "Follow-up duration for primary endpoint(s) in months", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Type of Study": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Type of follow-up given", "Column 6": "Follow-up duration for primary endpoint(s) in months", "Column 7": "Primary Endpoint", "Column 8": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 9": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 10": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details."}}</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4104,17 +3394,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Type of follow-up given"}}</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Type of follow-up given", "Column 6": "Study name", "Column 7": "Cancer type", "Column 8": "Name of ICI", "Column 9": "Primary endpoint", "Column 10": "Follow-up duration for primary endpoint(s) in months"}}</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Original/Follow Up", "Column 6": "Type of follow-up given", "Column 7": "Follow-up duration for primary endpoint(s) in months", "Column 8": "Primary endpoint", "Column 9": "Cancer type", "Column 10": "Study name"}}</t>
+          <t>{"selected_filter": {"Type of Study": "Follow-up"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Type of follow-up given", "Column 6": "Follow-up duration for primary endpoint(s) in months", "Column 7": "Primary Endpoint", "Column 8": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 9": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 10": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details."}}</t>
         </is>
       </c>
     </row>
@@ -4145,27 +3425,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Included in MA": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 7": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned).", "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."}}</t>
+          <t>{"selected_filter": {"Included in MA": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Included in MA": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Included in MA": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>{"selected_filter": {"Included in MA": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Included in MA": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Included in MA": "Yes"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary endpoint"}}</t>
         </is>
       </c>
     </row>
@@ -4201,22 +3471,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Included in MA": "No"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Included in MA": "No"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary endpoint", "Column 8": "Trial phase", "Column 9": "Type of combination", "Column 10": "Control regimen"}}</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Included in MA": "No"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Included in MA": "No"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Control regimen", "Column 9": "Clinical Setting in relation to surgery", "Column 10": "Primary endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Included in MA": "No"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary endpoint"}}</t>
+          <t>{"selected_filter": {"Included in MA": "No"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary endpoint", "Column 8": "Trial phase", "Column 9": "Type of combination", "Column 10": "Control regimen"}}</t>
         </is>
       </c>
     </row>
@@ -4230,7 +3490,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "Renal Cell Carcinoma",
+    "Cancer Type": "Renal Cell Carcinoma (RCC)",
     "Type of Study": "Original publication"
   },
   "selected_column": {
@@ -4252,22 +3512,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "Type of Study": "Original publication"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "Type of Study": "Original publication"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "Type of Study": "Original publication"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Monotherapy/combination", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "Type of Study": "Original publication"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Trial phase", "Column 10": "Treatment regimen"}}</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "Type of Study": "Original publication"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "Type of Study": "Original publication"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
     </row>
@@ -4283,7 +3533,7 @@
   "selected_filter": {
     "Cancer Type": "Gastric/GEJ",
     "Trial Phase": "Phase 3",
-    "Class of ICI": "PD-L1"
+    "ICI Class": "PD-L1"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -4300,27 +3550,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "Trial Phase": "Phase 3", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Total sample size", "Column 10": "Monotherapy/combination"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "Trial Phase": "Phase 3", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Monotherapy/combination"}}</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "Trial Phase": "Phase 3", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Total sample size", "Column 10": "Monotherapy/combination"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "Trial Phase": "Phase 3", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Monotherapy/combination"}}</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "Trial Phase": "Phase 3", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Monotherapy/combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "Trial Phase": "Phase 3", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "ICI Class": "PD-L1", "Trial Phase": "Phase 3"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Primary Endpoint", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "Trial Phase": "Phase 3", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Monotherapy/combination"}}</t>
         </is>
       </c>
     </row>
@@ -4335,7 +3575,7 @@
           <t>{
   "selected_filter": {
     "Cancer Type": "Esophageal/GEJ",
-    "Class of ICI": "PD1"
+    "ICI Class": "PD-1"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -4352,27 +3592,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Esophageal/GEJ", "ICI Class": "PD1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Clinical setting in relation to surgery", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Esophageal/GEJ", "ICI Class": "PD-1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Esophageal/GEJ", "ICI Class": "PD1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Primary Endpoint", "Column 8": "Clinical Setting in relation to surgery", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Esophageal/GEJ", "ICI Class": "PD-1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Esophageal/GEJ", "ICI Class": "PD1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Esophageal/GEJ", "ICI Class": "PD1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Esophageal/GEJ", "ICI Class": "PD1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Esophageal/GEJ", "ICI Class": "PD-1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
     </row>
@@ -4386,7 +3616,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "Small Cell Lung Cancer"
+    "Cancer Type": "Small Cell Lung Cancer (SCLC)"
   },
   "selected_column": {
     "Column 1": "Study name",
@@ -4403,27 +3633,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Small Cell Lung Cancer (SCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Small Cell Lung Cancer (SCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Small Cell Lung Cancer (SCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Small Cell Lung Cancer (SCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Small Cell Lung Cancer (SCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Small Cell Lung Cancer (SCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Small Cell Lung Cancer (SCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Small Cell Lung Cancer (SCLC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
     </row>
@@ -4437,8 +3657,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "Head and Neck",
-    "Primary endpoint": "OS"
+    "Cancer Type": "Head and Neck (HNSCC)",
+    "Primary Endpoint": "OS"
   },
   "selected_column": {
     "Column 1": "Study name",
@@ -4455,27 +3675,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Name of ICI", "Column 10": "Monotherapy/combination"}}</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Name of ICI", "Column 8": "Monotherapy/combination", "Column 9": "Type of combination", "Column 10": "Control regimen"}}</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Total sample size", "Column 10": "Clinical Setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Trial phase", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "Primary Endpoint": "OS (Overall Survival)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Trial phase", "Column 7": "Name of ICI", "Column 8": "Monotherapy/combination", "Column 9": "Type of combination", "Column 10": "Control regimen"}}</t>
         </is>
       </c>
     </row>
@@ -4489,7 +3699,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "Head and Neck"
+    "Cancer Type": "Head and Neck (HNSCC)"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -4506,27 +3716,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Primary Endpoint", "Column 8": "Monotherapy/combination", "Column 9": "Treatment regimen", "Column 10": "Control regimen"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Primary Endpoint", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Type of Therapy", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Monotherapy/combination"}}</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Primary Endpoint", "Column 9": "Treatment regimen", "Column 10": "Control regimen"}}</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Trial phase", "Column 7": "Type of Therapy", "Column 8": "Primary Endpoint", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
     </row>
@@ -4562,22 +3762,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>{"selected_filter": {"Cancer Type": "Breast"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Trial phase"}}</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>{"selected_filter": {"Cancer Type": "Breast"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Breast"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Breast"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Breast"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical Setting in relation to surgery"}}</t>
         </is>
       </c>
     </row>
@@ -4609,27 +3799,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "Clinical Setting": "Metastatic / Recurrent (Unresectable)", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "Clinical Setting": "Metastatic / Recurrent (Unresectable)", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "Clinical Setting": "Metastatic / Recurrent (Unresectable)", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "Clinical Setting": "Metastatic / Recurrent (Unresectable)", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Total sample size", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "Clinical Setting": "Metastatic / Recurrent (Unresectable)", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Monotherapy/combination", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Gastric/GEJ", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -4643,7 +3823,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "Hepatocellular carcinoma"
+    "Cancer Type": "Hepatocellular carcinoma (HCC)"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -4660,27 +3840,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Lines of treatment", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Lines of treatment", "Column 9": "Primary Endpoint", "Column 10": "Monotherapy/combination"}}</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Lines of treatment", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Lines of treatment", "Column 9": "Primary Endpoint", "Column 10": "Monotherapy/combination"}}</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Lines of treatment", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Lines of treatment", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Lines of treatment", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Monotherapy/combination"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Hepatocellular carcinoma (HCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Lines of treatment", "Column 9": "Primary Endpoint", "Column 10": "Monotherapy/combination"}}</t>
         </is>
       </c>
     </row>
@@ -4694,7 +3864,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "Renal Cell Carcinoma"
+    "Cancer Type": "Renal Cell Carcinoma (RCC)"
   },
   "selected_column": {
     "Column 1": "Lines of treatment",
@@ -4711,27 +3881,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Control regimen", "Column 9": "Lines of treatment", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Lines of treatment", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Monotherapy/combination", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Control regimen", "Column 7": "Monotherapy/combination", "Column 8": "Lines of treatment", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Lines of treatment", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Monotherapy/combination", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Lines of treatment", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Lines of treatment", "Column 6": "Primary Endpoint", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Monotherapy/combination"}}</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Clinical setting in relation to surgery", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Lines of treatment"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Lines of treatment", "Column 8": "Clinical setting in relation to surgery", "Column 9": "Primary Endpoint", "Column 10": "Control regimen"}}</t>
         </is>
       </c>
     </row>
@@ -4762,27 +3922,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Clinical setting in relation to surgery": "Perioperative"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Monotherapy/combination", "Column 9": "Type of combination", "Column 10": "Primary endpoint"}}</t>
+          <t>{"selected_filter": {"Clinical setting in relation to surgery": "Perioperative"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Clinical setting in relation to surgery": "Perioperative"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Clinical setting in relation to surgery": "Perioperative"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Clinical setting in relation to surgery": "Perioperative"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Total sample size", "Column 10": "Primary endpoint"}}</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Clinical setting in relation to surgery": "Perioperative"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Clinical setting in relation to surgery": "Perioperative"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Clinical setting in relation to surgery": "Perioperative"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -4796,7 +3946,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "NSCLC",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
     "Lines of treatment": "2L"
   },
   "selected_column": {
@@ -4814,27 +3964,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting": "Metastatic / Recurrent (Unresectable)", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Clinical Setting in relation to surgery", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Clinical Setting": "Metastatic / Recurrent (Unresectable)", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Trial phase", "Column 7": "Control regimen", "Column 8": "Monotherapy/combination", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Lines of treatment": "2L"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
     </row>
@@ -4865,27 +4005,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Class of ICI", "Column 6": "Name of ICI", "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 8": "Primary endpoint", "Column 9": "Monotherapy/combination", "Column 10": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos."}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Class of ICI", "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 9": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."}}</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 8": "Monotherapy/combination", "Column 9": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 10": "Clinical setting in relation to surgery – Where the therapy sits on the surgical timeline:\n\tNeoadjuvant (before surgery),\n\tAdjuvant (after surgery),\n\tPerioperative (pre- and post-op plan),\n\tMaintenance (post–initial therapy to maintain response),\n\tMetastatic/recurrent (unresectable) (no curative surgery planned)."}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Class of ICI", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Trial phase", "Column 9": "Primary endpoint", "Column 10": "Type of combination"}}</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Class of ICI", "Column 6": "Name of ICI", "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 8": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details.", "Column 9": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR).", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms."}}</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Class of ICI", "Column 6": "Name of ICI", "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 8": "Primary Endpoint", "Column 9": "Monotherapy/combination", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 8": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination).", "Column 9": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 10": "Treatment regimen – The full, prespecified therapy given to the experimental arm(s): drug names, doses, schedules, cycles, and any radiation/surgery/ADT details."}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Class of ICI", "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Type of combination – If combination, specify the partner(s): e.g., ICI + chemotherapy, ICI + targeted therapy, ICI + hormone therapy, ICI + another ICI (dual ICI), ICI + radiotherapy, or triplet/multimodal combos.", "Column 9": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 10": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)."}}</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4029,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Type of combination": "ICI + MEKi"
+    "Type of combination (Treatment Arm)": "ICI + MEKi"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -4916,27 +4046,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + MEKi"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Primary Endpoint", "Column 9": "Control regimen", "Column 10": "Treatment regimen"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + MEKi"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + MEKi"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Primary endpoint", "Column 9": "Trial phase", "Column 10": "Study name"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + MEKi"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + MEKi"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + MEKi"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + MEKi"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Type of combination (Treatment Arm)": "ICI + MEKi"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4070,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "NSCLC"
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -4967,27 +4087,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "ICI Class": "PD-1", "Trial Phase": "Phase 3"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "ICI Class": "PD1", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "ICI Class": "PD-1", "Trial Phase": "Phase 3"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Clinical Setting in relation to surgery", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "ICI Class": "PD-L1"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "ICI Class": "PD1", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Total sample size", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Lines of treatment"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "ICI Class": "PD-1", "Trial Phase": "Phase 3"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
     </row>
@@ -5018,27 +4128,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Primary Endpoint", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Primary Endpoint", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Primary Endpoint", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Monotherapy/combination", "Column 7": "Primary Endpoint", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
     </row>
@@ -5052,7 +4152,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "Head and Neck"
+    "Cancer Type": "Head and Neck (HNSCC)"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -5069,25 +4169,15 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Clinical setting in relation to surgery", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
         <is>
           <t>{"selected_filter": {"Cancer Type": "Head and Neck (HNSCC)", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
         </is>
@@ -5103,7 +4193,7 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "NSCLC",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
     "Is PD-L1 positivity inclusion criteria": "No"
   },
   "selected_column": {
@@ -5121,27 +4211,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Is PD-L1 positivity inclusion criteria": "No"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Clinical Setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Is PD-L1 positivity inclusion criteria": "No"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Is PD-L1 positivity inclusion criteria": "No"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Type of Therapy", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Is PD-L1 positivity inclusion criteria": "No"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Trial phase", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Is PD-L1 positivity inclusion criteria": "No"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Is PD-L1 positivity inclusion criteria": "No"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Clinical Setting in relation to surgery", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Is PD-L1 positivity inclusion criteria": "No"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of Therapy", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Primary Endpoint"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Is PD-L1 positivity inclusion criteria": "No"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Class of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Type of combination", "Column 9": "Control regimen", "Column 10": "Primary Endpoint"}}</t>
         </is>
       </c>
     </row>
@@ -5171,27 +4251,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Trial Phase": "Phase 3"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Control regimen"}}</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Trial Phase": "Phase 3"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Primary Endpoint", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Treatment regimen"}}</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Trial Phase": "Phase 3"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Trial Phase": "Phase 3"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Primary Endpoint", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -5205,8 +4275,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "Renal Cell Carcinoma",
-    "Type of combination": "ICI + TKI"
+    "Cancer Type": "Renal Cell Carcinoma (RCC)",
+    "Type of combination (Treatment Arm)": "ICI + TKI"
   },
   "selected_column": {
     "Column 1": "Treatment regimen",
@@ -5223,27 +4293,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Total sample size", "Column 9": "Primary Endpoint", "Column 10": "Type of combination"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "Type of Therapy": "Combination Therapy", "Type of combination (Treatment Arm)": "ICI + Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Clinical setting in relation to surgery", "Column 9": "Total sample size", "Column 10": "Primary Endpoint"}}</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "Type of combination (Treatment Arm)": "ICI + Anti-VEGF"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Renal Cell Carcinoma (RCC)", "Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -5257,8 +4317,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "Small Cell Lung Cancer",
-    "Type of combination": "ICI + Chemo"
+    "Cancer Type": "Small Cell Lung Cancer (SCLC)",
+    "Type of combination (Treatment Arm)": "ICI + Chemo"
   },
   "selected_column": {
     "Column 1": "Treatment regimen",
@@ -5275,27 +4335,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Small Cell Lung Cancer (SCLC)", "Type of Therapy": "Combination Therapy", "Type of combination (Treatment Arm)": "ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Control regimen", "Column 7": "Trial phase", "Column 8": "Primary Endpoint", "Column 9": "Monotherapy/combination", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Small Cell Lung Cancer (SCLC)", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Small Cell Lung Cancer (SCLC)", "Type of combination (Treatment Arm)": "ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Small Cell Lung Cancer (SCLC)", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Small Cell Lung Cancer (SCLC)", "Type of combination (Treatment Arm)": "ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Control regimen", "Column 8": "Total sample size", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Small Cell Lung Cancer (SCLC)", "Type of combination (Treatment Arm)": "ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Control regimen", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Small Cell Lung Cancer (SCLC)", "Type of Therapy": "Combination Therapy", "Type of combination (Treatment Arm)": "ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Trial phase", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Small Cell Lung Cancer (SCLC)", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -5309,8 +4359,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "NSCLC",
-    "Type of combination": "ICI + ICI + Chemo"
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
   },
   "selected_column": {
     "Column 1": "Treatment regimen",
@@ -5327,27 +4377,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Monotherapy/combination"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Monotherapy/combination"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -5377,27 +4417,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Year": "2010"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab)", "Column 7": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination)", "Column 8": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)", "Column 9": "Trial phase", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms"}}</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Primary endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab)", "Column 7": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination)", "Column 8": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)", "Column 9": "Trial phase", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms"}}</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Class of ICI", "Column 8": "Type of Therapy", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Monotherapy/combination", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Year": "2010"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Primary Endpoint", "Column 8": "Monotherapy/combination", "Column 9": "Treatment regimen", "Column 10": "Control regimen"}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant", "Column 6": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab)", "Column 7": "Monotherapy/combination – Whether the ICI is given alone (monotherapy) or with other anticancer treatments (combination)", "Column 8": "Primary endpoint – The prespecified main outcome the trial is powered to test (e.g., OS, PFS, pCR, EFS, RFS/DFS, ORR)", "Column 9": "Trial phase", "Column 10": "Total sample size – Total number of participants randomized/enrolled for analysis across all arms"}}</t>
         </is>
       </c>
     </row>
@@ -5411,8 +4441,8 @@
         <is>
           <t>{
   "selected_filter": {
-    "Cancer Type": "NSCLC",
-    "Type of combination": "ICI + ICI"
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
   },
   "selected_column": {
     "Column 1": "Treatment regimen",
@@ -5429,27 +4459,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Treatment regimen", "Column 7": "Control regimen", "Column 8": "Trial phase", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Primary Endpoint", "Column 8": "Clinical Setting in relation to surgery", "Column 9": "Trial phase", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Control regimen", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Primary Endpoint", "Column 7": "Control regimen", "Column 8": "Trial phase", "Column 9": "Monotherapy/combination", "Column 10": "Clinical Setting in relation to surgery"}}</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Control regimen", "Column 7": "Clinical setting in relation to surgery", "Column 8": "Primary Endpoint", "Column 9": "Total sample size", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Control regimen", "Column 7": "Primary Endpoint", "Column 8": "Trial phase", "Column 9": "Monotherapy/combination", "Column 10": "Lines of treatment"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)", "Type of combination (Treatment Arm)": "ICI + ICI"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Name of ICI", "Column 6": "Type of combination", "Column 7": "Control regimen", "Column 8": "Primary Endpoint", "Column 9": "Trial phase", "Column 10": "Clinical setting in relation to surgery"}}</t>
         </is>
       </c>
     </row>
@@ -5480,27 +4500,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Lines of treatment": "≥3L", "Type of Therapy": "Combination Therapy"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Treatment regimen", "Column 7": "Name of ICI", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
+          <t>{"selected_filter": {"Lines of treatment": "2L+"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Clinical Setting": "Metastatic / Recurrent (Unresectable)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Lines of treatment", "Column 9": "Primary Endpoint", "Column 10": "Control regimen"}}</t>
+          <t>{"selected_filter": {"Lines of treatment": "2L+"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Clinical Setting": "Metastatic / Recurrent (Unresectable)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of Therapy", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Lines of treatment"}}</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Lines of treatment": "3L+"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Primary endpoint", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Clinical Setting": "Metastatic / Recurrent (Unresectable)"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Treatment regimen", "Column 8": "Monotherapy/combination", "Column 9": "Control regimen", "Column 10": "Lines of treatment"}}</t>
+          <t>{"selected_filter": {"Lines of treatment": "2L+"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Cancer type", "Column 6": "Name of ICI", "Column 7": "Type of combination", "Column 8": "Control regimen", "Column 9": "Primary endpoint", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
     </row>
@@ -5528,27 +4538,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months", "Column 6": "Cancer type", "Column 7": "Treatment regimen", "Column 8": "Name of ICI", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Primary endpoint"}}</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Treatment regimen", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Total sample size"}}</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Type of Therapy", "Column 9": "Primary Endpoint", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months", "Column 6": "Cancer type", "Column 7": "Treatment regimen", "Column 8": "Name of ICI", "Column 9": "Monotherapy/combination", "Column 10": "Total sample size"}}</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months [Overall]", "Column 6": "Cancer type – The specific disease/indication under study (e.g., metastatic castration-sensitive prostate cancer, NSCLC, melanoma), including stage/setting when relevant.", "Column 7": "Name of ICI – The exact immune checkpoint inhibitor used (e.g., pembrolizumab, nivolumab, atezolizumab, ipilimumab).", "Column 8": "Control regimen – The comparator treatment assigned to the control group (e.g., placebo, best supportive care, standard of care chemo X, ADT alone, physician’s choice).", "Column 9": "Clinical setting in relation to surgery", "Column 10": "Type of Study"}}</t>
+          <t>{"selected_filter": {}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Follow-up duration for primary endpoint(s) in months", "Column 6": "Cancer type", "Column 7": "Name of ICI", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Primary endpoint"}}</t>
         </is>
       </c>
     </row>
@@ -5563,7 +4563,7 @@
           <t>{
   "selected_filter": {
     "Cancer Type": "Melanoma",
-    "Name of ICI": "Pembrolizumab",
+    "ICI Name": "Pembrolizumab",
     "Clinical Setting": "Adjuvant"
   },
   "selected_column": {
@@ -5579,27 +4579,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Clinical Setting": "Adjuvant", "Name of ICI": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Name of ICI", "Column 7": "Monotherapy/combination", "Column 8": "Control regimen", "Column 9": "Total sample size", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Clinical Setting": "Adjuvant", "ICI Name": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Primary Endpoint", "Column 7": "Total sample size", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Monotherapy/combination"}}</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Clinical Setting": "Adjuvant", "Name of ICI": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Primary Endpoint", "Column 7": "Total sample size", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Clinical Setting": "Adjuvant", "ICI Name": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Primary Endpoint", "Column 7": "Total sample size", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Monotherapy/combination"}}</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Clinical Setting": "Adjuvant", "Name of ICI": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Total sample size", "Column 7": "Monotherapy/combination", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Clinical Setting": "Adjuvant", "Name of ICI": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Primary Endpoint", "Column 7": "Total sample size", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Monotherapy/combination"}}</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Clinical Setting": "Adjuvant", "Name of ICI": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Primary Endpoint", "Column 6": "Total sample size", "Column 7": "Treatment regimen", "Column 8": "Control regimen", "Column 9": "Monotherapy/combination", "Column 10": "Clinical setting in relation to surgery"}}</t>
+          <t>{"selected_filter": {"Cancer Type": "Melanoma", "Clinical Setting": "Adjuvant", "ICI Name": "Pembrolizumab"}, "selected_column": {"Column 1": "NCT", "Column 2": "PMID", "Column 3": "Authors", "Column 4": "Year", "Column 5": "Study name", "Column 6": "Primary Endpoint", "Column 7": "Total sample size", "Column 8": "Treatment regimen", "Column 9": "Control regimen", "Column 10": "Trial phase"}}</t>
         </is>
       </c>
     </row>
@@ -5614,7 +4604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5643,16 +4633,6 @@
           <t>run_3_time_sec</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>run_4_time_sec</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>run_5_time_sec</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -5664,19 +4644,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.221653699874878</v>
+        <v>1.539659976959229</v>
       </c>
       <c r="D2" t="n">
-        <v>1.394677877426147</v>
+        <v>1.581015586853027</v>
       </c>
       <c r="E2" t="n">
-        <v>1.461922645568848</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.505573749542236</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.659163236618042</v>
+        <v>1.418828010559082</v>
       </c>
     </row>
     <row r="3">
@@ -5689,19 +4663,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.455246210098267</v>
+        <v>1.408358812332153</v>
       </c>
       <c r="D3" t="n">
-        <v>1.459401369094849</v>
+        <v>1.463405132293701</v>
       </c>
       <c r="E3" t="n">
-        <v>1.537572383880615</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.416521072387695</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.47617506980896</v>
+        <v>1.358636617660522</v>
       </c>
     </row>
     <row r="4">
@@ -5714,19 +4682,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.139233350753784</v>
+        <v>1.442944526672363</v>
       </c>
       <c r="D4" t="n">
-        <v>1.153987646102905</v>
+        <v>1.288354635238647</v>
       </c>
       <c r="E4" t="n">
-        <v>1.447227954864502</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.328055858612061</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.419490575790405</v>
+        <v>1.450298309326172</v>
       </c>
     </row>
     <row r="5">
@@ -5739,19 +4701,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.537989616394043</v>
+        <v>1.575614213943481</v>
       </c>
       <c r="D5" t="n">
-        <v>1.465659618377686</v>
+        <v>1.449898958206177</v>
       </c>
       <c r="E5" t="n">
-        <v>1.556537628173828</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.470730543136597</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.510830402374268</v>
+        <v>1.52321720123291</v>
       </c>
     </row>
     <row r="6">
@@ -5764,19 +4720,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.341646194458008</v>
+        <v>1.426322937011719</v>
       </c>
       <c r="D6" t="n">
-        <v>1.493402719497681</v>
+        <v>1.428318977355957</v>
       </c>
       <c r="E6" t="n">
-        <v>1.371883630752563</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.435814619064331</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.377959966659546</v>
+        <v>1.508764982223511</v>
       </c>
     </row>
     <row r="7">
@@ -5789,19 +4739,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.184124231338501</v>
+        <v>1.358046054840088</v>
       </c>
       <c r="D7" t="n">
-        <v>1.382238149642944</v>
+        <v>1.4089515209198</v>
       </c>
       <c r="E7" t="n">
-        <v>1.526614189147949</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.521851539611816</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.341231346130371</v>
+        <v>1.312757968902588</v>
       </c>
     </row>
     <row r="8">
@@ -5814,19 +4758,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.248088121414185</v>
+        <v>1.253976345062256</v>
       </c>
       <c r="D8" t="n">
-        <v>1.241422176361084</v>
+        <v>1.213303089141846</v>
       </c>
       <c r="E8" t="n">
-        <v>1.551751613616943</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.232919454574585</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.354695796966553</v>
+        <v>1.294766664505005</v>
       </c>
     </row>
     <row r="9">
@@ -5839,19 +4777,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.95881199836731</v>
+        <v>1.976945877075195</v>
       </c>
       <c r="D9" t="n">
-        <v>1.75920033454895</v>
+        <v>1.232996463775635</v>
       </c>
       <c r="E9" t="n">
-        <v>1.886638879776001</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.712210178375244</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.153015851974487</v>
+        <v>2.170847415924072</v>
       </c>
     </row>
     <row r="10">
@@ -5864,19 +4796,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.349891662597656</v>
+        <v>1.336935758590698</v>
       </c>
       <c r="D10" t="n">
-        <v>2.775738716125488</v>
+        <v>2.160706281661987</v>
       </c>
       <c r="E10" t="n">
-        <v>2.570616483688354</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.374972581863403</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.46006178855896</v>
+        <v>2.107112169265747</v>
       </c>
     </row>
     <row r="11">
@@ -5889,19 +4815,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.918134927749634</v>
+        <v>1.236467599868774</v>
       </c>
       <c r="D11" t="n">
-        <v>1.178975105285645</v>
+        <v>1.159976243972778</v>
       </c>
       <c r="E11" t="n">
-        <v>1.918361186981201</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.108062982559204</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.519186973571777</v>
+        <v>1.165281772613525</v>
       </c>
     </row>
     <row r="12">
@@ -5914,19 +4834,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.374907493591309</v>
+        <v>1.400884866714478</v>
       </c>
       <c r="D12" t="n">
-        <v>1.464379787445068</v>
+        <v>1.226270198822021</v>
       </c>
       <c r="E12" t="n">
-        <v>1.305912256240845</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.365954637527466</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.363412618637085</v>
+        <v>1.203112602233887</v>
       </c>
     </row>
     <row r="13">
@@ -5939,19 +4853,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.365823984146118</v>
+        <v>1.302361726760864</v>
       </c>
       <c r="D13" t="n">
-        <v>2.668643712997437</v>
+        <v>1.254496812820435</v>
       </c>
       <c r="E13" t="n">
-        <v>1.438318490982056</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.393500089645386</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.44989013671875</v>
+        <v>1.43177318572998</v>
       </c>
     </row>
     <row r="14">
@@ -5964,19 +4872,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.420726299285889</v>
+        <v>1.300010681152344</v>
       </c>
       <c r="D14" t="n">
-        <v>1.368228912353516</v>
+        <v>1.361120223999023</v>
       </c>
       <c r="E14" t="n">
-        <v>1.348512887954712</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1.482589244842529</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.367514133453369</v>
+        <v>1.282432079315186</v>
       </c>
     </row>
     <row r="15">
@@ -5989,19 +4891,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.631835222244263</v>
+        <v>1.262424468994141</v>
       </c>
       <c r="D15" t="n">
-        <v>2.639565467834473</v>
+        <v>1.350076913833618</v>
       </c>
       <c r="E15" t="n">
-        <v>2.632594108581543</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.545315265655518</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2.869125604629517</v>
+        <v>2.498024940490723</v>
       </c>
     </row>
     <row r="16">
@@ -6014,19 +4910,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.478124380111694</v>
+        <v>1.542065382003784</v>
       </c>
       <c r="D16" t="n">
-        <v>1.406829595565796</v>
+        <v>1.410043954849243</v>
       </c>
       <c r="E16" t="n">
-        <v>1.456290721893311</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.348248243331909</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.525557041168213</v>
+        <v>1.303313016891479</v>
       </c>
     </row>
     <row r="17">
@@ -6039,19 +4929,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.421208381652832</v>
+        <v>1.330563306808472</v>
       </c>
       <c r="D17" t="n">
-        <v>1.514993906021118</v>
+        <v>1.351776599884033</v>
       </c>
       <c r="E17" t="n">
-        <v>1.732260942459106</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1.487773895263672</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.576073408126831</v>
+        <v>1.39809513092041</v>
       </c>
     </row>
     <row r="18">
@@ -6064,19 +4948,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.320490598678589</v>
+        <v>1.3094162940979</v>
       </c>
       <c r="D18" t="n">
-        <v>1.24947190284729</v>
+        <v>1.313488721847534</v>
       </c>
       <c r="E18" t="n">
-        <v>1.329973459243774</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1.434403419494629</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.719322443008423</v>
+        <v>1.349759817123413</v>
       </c>
     </row>
     <row r="19">
@@ -6089,19 +4967,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.392117738723755</v>
+        <v>2.499807834625244</v>
       </c>
       <c r="D19" t="n">
-        <v>2.925209522247314</v>
+        <v>1.37472939491272</v>
       </c>
       <c r="E19" t="n">
-        <v>2.383171558380127</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1.722399234771729</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.493479251861572</v>
+        <v>2.233572006225586</v>
       </c>
     </row>
     <row r="20">
@@ -6114,19 +4986,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.413663387298584</v>
+        <v>1.265191316604614</v>
       </c>
       <c r="D20" t="n">
-        <v>1.295782804489136</v>
+        <v>1.393574953079224</v>
       </c>
       <c r="E20" t="n">
-        <v>1.548733711242676</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1.396053314208984</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.388187170028687</v>
+        <v>1.240626335144043</v>
       </c>
     </row>
     <row r="21">
@@ -6139,19 +5005,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.44529914855957</v>
+        <v>1.338297367095947</v>
       </c>
       <c r="D21" t="n">
-        <v>1.473258972167969</v>
+        <v>1.379431962966919</v>
       </c>
       <c r="E21" t="n">
-        <v>1.357487916946411</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1.503307104110718</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.481459617614746</v>
+        <v>1.286467790603638</v>
       </c>
     </row>
     <row r="22">
@@ -6164,19 +5024,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.308719158172607</v>
+        <v>1.26017951965332</v>
       </c>
       <c r="D22" t="n">
-        <v>1.413074254989624</v>
+        <v>1.281077861785889</v>
       </c>
       <c r="E22" t="n">
-        <v>1.411990404129028</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1.428432941436768</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.474181175231934</v>
+        <v>1.410886287689209</v>
       </c>
     </row>
     <row r="23">
@@ -6189,19 +5043,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.532124280929565</v>
+        <v>1.477212905883789</v>
       </c>
       <c r="D23" t="n">
-        <v>1.421618223190308</v>
+        <v>1.462054967880249</v>
       </c>
       <c r="E23" t="n">
-        <v>1.380887031555176</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.54923152923584</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1.614274024963379</v>
+        <v>1.411505937576294</v>
       </c>
     </row>
     <row r="24">
@@ -6214,19 +5062,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.460031747817993</v>
+        <v>1.243587493896484</v>
       </c>
       <c r="D24" t="n">
-        <v>1.474363327026367</v>
+        <v>1.290812969207764</v>
       </c>
       <c r="E24" t="n">
-        <v>1.419808626174927</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1.370524644851685</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.411501169204712</v>
+        <v>1.200178384780884</v>
       </c>
     </row>
     <row r="25">
@@ -6239,19 +5081,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.454681873321533</v>
+        <v>1.225954532623291</v>
       </c>
       <c r="D25" t="n">
-        <v>1.262316465377808</v>
+        <v>1.430033445358276</v>
       </c>
       <c r="E25" t="n">
-        <v>1.630692481994629</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1.265527009963989</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.374640941619873</v>
+        <v>1.35522198677063</v>
       </c>
     </row>
     <row r="26">
@@ -6264,19 +5100,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.441519260406494</v>
+        <v>1.498363018035889</v>
       </c>
       <c r="D26" t="n">
-        <v>1.346545934677124</v>
+        <v>1.412880420684814</v>
       </c>
       <c r="E26" t="n">
-        <v>1.637706279754639</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1.43000054359436</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.325517416000366</v>
+        <v>1.563337802886963</v>
       </c>
     </row>
     <row r="27">
@@ -6289,19 +5119,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.338693857192993</v>
+        <v>1.226703405380249</v>
       </c>
       <c r="D27" t="n">
-        <v>1.29395866394043</v>
+        <v>1.240231275558472</v>
       </c>
       <c r="E27" t="n">
-        <v>1.478738784790039</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1.402048349380493</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.347701549530029</v>
+        <v>1.324148178100586</v>
       </c>
     </row>
     <row r="28">
@@ -6314,19 +5138,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.448748111724854</v>
+        <v>1.357215166091919</v>
       </c>
       <c r="D28" t="n">
-        <v>2.489124774932861</v>
+        <v>1.227947235107422</v>
       </c>
       <c r="E28" t="n">
-        <v>1.348705768585205</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1.724623203277588</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1.44739818572998</v>
+        <v>1.231728076934814</v>
       </c>
     </row>
     <row r="29">
@@ -6339,19 +5157,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.33726954460144</v>
+        <v>1.248284816741943</v>
       </c>
       <c r="D29" t="n">
-        <v>1.251589298248291</v>
+        <v>1.208990812301636</v>
       </c>
       <c r="E29" t="n">
-        <v>1.285841464996338</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1.291245937347412</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.272449493408203</v>
+        <v>1.254091262817383</v>
       </c>
     </row>
     <row r="30">
@@ -6364,19 +5176,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.353001117706299</v>
+        <v>1.39328408241272</v>
       </c>
       <c r="D30" t="n">
-        <v>1.505724668502808</v>
+        <v>1.731076240539551</v>
       </c>
       <c r="E30" t="n">
-        <v>1.345011234283447</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.435397624969482</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.428522348403931</v>
+        <v>1.380486488342285</v>
       </c>
     </row>
     <row r="31">
@@ -6389,19 +5195,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.631309986114502</v>
+        <v>1.321350812911987</v>
       </c>
       <c r="D31" t="n">
-        <v>1.217232465744019</v>
+        <v>1.296693325042725</v>
       </c>
       <c r="E31" t="n">
-        <v>2.757678031921387</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2.323507308959961</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.237604856491089</v>
+        <v>1.230079650878906</v>
       </c>
     </row>
     <row r="32">
@@ -6414,19 +5214,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.177161455154419</v>
+        <v>1.207411050796509</v>
       </c>
       <c r="D32" t="n">
-        <v>1.281080484390259</v>
+        <v>1.309333801269531</v>
       </c>
       <c r="E32" t="n">
-        <v>1.291457176208496</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1.39467453956604</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.269775152206421</v>
+        <v>1.36466383934021</v>
       </c>
     </row>
     <row r="33">
@@ -6439,19 +5233,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.354175329208374</v>
+        <v>1.267148971557617</v>
       </c>
       <c r="D33" t="n">
-        <v>1.285897493362427</v>
+        <v>1.298762083053589</v>
       </c>
       <c r="E33" t="n">
-        <v>1.252850770950317</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1.308043956756592</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1.370965957641602</v>
+        <v>1.415136098861694</v>
       </c>
     </row>
     <row r="34">
@@ -6464,19 +5252,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2.144862174987793</v>
+        <v>2.201930284500122</v>
       </c>
       <c r="D34" t="n">
-        <v>2.560178279876709</v>
+        <v>2.229722261428833</v>
       </c>
       <c r="E34" t="n">
-        <v>1.908536195755005</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1.381297588348389</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1.292086839675903</v>
+        <v>1.402361154556274</v>
       </c>
     </row>
     <row r="35">
@@ -6489,19 +5271,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.679292440414429</v>
+        <v>1.462892055511475</v>
       </c>
       <c r="D35" t="n">
-        <v>1.507705450057983</v>
+        <v>1.407370090484619</v>
       </c>
       <c r="E35" t="n">
-        <v>1.457646608352661</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1.786858797073364</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1.410761833190918</v>
+        <v>1.299720287322998</v>
       </c>
     </row>
     <row r="36">
@@ -6514,19 +5290,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2.146622896194458</v>
+        <v>1.581332445144653</v>
       </c>
       <c r="D36" t="n">
-        <v>1.560811996459961</v>
+        <v>1.301594734191895</v>
       </c>
       <c r="E36" t="n">
-        <v>1.351249694824219</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1.495760202407837</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1.458462238311768</v>
+        <v>1.402268409729004</v>
       </c>
     </row>
     <row r="37">
@@ -6539,19 +5309,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.270376682281494</v>
+        <v>1.167210102081299</v>
       </c>
       <c r="D37" t="n">
-        <v>1.311633348464966</v>
+        <v>1.209722757339478</v>
       </c>
       <c r="E37" t="n">
-        <v>1.335337400436401</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1.224822282791138</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1.308205604553223</v>
+        <v>1.260905027389526</v>
       </c>
     </row>
     <row r="38">
@@ -6564,19 +5328,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.304903507232666</v>
+        <v>1.208502769470215</v>
       </c>
       <c r="D38" t="n">
-        <v>1.456081628799438</v>
+        <v>1.204246044158936</v>
       </c>
       <c r="E38" t="n">
-        <v>1.442919731140137</v>
-      </c>
-      <c r="F38" t="n">
-        <v>2.506232500076294</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1.743908643722534</v>
+        <v>1.191226720809937</v>
       </c>
     </row>
     <row r="39">
@@ -6589,19 +5347,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.23380708694458</v>
+        <v>1.194637537002563</v>
       </c>
       <c r="D39" t="n">
-        <v>1.302611351013184</v>
+        <v>1.30579948425293</v>
       </c>
       <c r="E39" t="n">
-        <v>1.306934833526611</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1.241705894470215</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1.289872407913208</v>
+        <v>1.201863527297974</v>
       </c>
     </row>
     <row r="40">
@@ -6614,19 +5366,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.301326513290405</v>
+        <v>1.379157543182373</v>
       </c>
       <c r="D40" t="n">
-        <v>1.592914342880249</v>
+        <v>1.242030620574951</v>
       </c>
       <c r="E40" t="n">
-        <v>1.253674983978271</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1.257110357284546</v>
-      </c>
-      <c r="G40" t="n">
-        <v>1.246953725814819</v>
+        <v>1.422529458999634</v>
       </c>
     </row>
     <row r="41">
@@ -6639,19 +5385,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.294329643249512</v>
+        <v>1.107508420944214</v>
       </c>
       <c r="D41" t="n">
-        <v>1.475116491317749</v>
+        <v>1.296160221099854</v>
       </c>
       <c r="E41" t="n">
-        <v>1.295177459716797</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1.235295057296753</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1.394104957580566</v>
+        <v>1.205543756484985</v>
       </c>
     </row>
     <row r="42">
@@ -6664,19 +5404,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.41286039352417</v>
+        <v>1.285928010940552</v>
       </c>
       <c r="D42" t="n">
-        <v>1.446781635284424</v>
+        <v>1.278150320053101</v>
       </c>
       <c r="E42" t="n">
-        <v>1.388082504272461</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1.217960119247437</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1.365686178207397</v>
+        <v>1.427554368972778</v>
       </c>
     </row>
     <row r="43">
@@ -6689,19 +5423,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.250714063644409</v>
+        <v>1.259300947189331</v>
       </c>
       <c r="D43" t="n">
-        <v>1.555214881896973</v>
+        <v>1.204049348831177</v>
       </c>
       <c r="E43" t="n">
-        <v>2.293999910354614</v>
-      </c>
-      <c r="F43" t="n">
-        <v>2.831584692001343</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2.324241399765015</v>
+        <v>1.206595182418823</v>
       </c>
     </row>
     <row r="44">
@@ -6714,19 +5442,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.279733180999756</v>
+        <v>1.301770448684692</v>
       </c>
       <c r="D44" t="n">
-        <v>1.394052267074585</v>
+        <v>1.114664793014526</v>
       </c>
       <c r="E44" t="n">
-        <v>1.184999704360962</v>
-      </c>
-      <c r="F44" t="n">
-        <v>1.272154569625854</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1.349131345748901</v>
+        <v>1.125773191452026</v>
       </c>
     </row>
     <row r="45">
@@ -6739,19 +5461,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.286903619766235</v>
+        <v>1.45487642288208</v>
       </c>
       <c r="D45" t="n">
-        <v>1.224035501480103</v>
+        <v>1.45344614982605</v>
       </c>
       <c r="E45" t="n">
-        <v>1.467416048049927</v>
-      </c>
-      <c r="F45" t="n">
-        <v>1.353508472442627</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1.370752573013306</v>
+        <v>1.273388624191284</v>
       </c>
     </row>
     <row r="46">
@@ -6764,19 +5480,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.337073087692261</v>
+        <v>1.373925924301147</v>
       </c>
       <c r="D46" t="n">
-        <v>1.400905132293701</v>
+        <v>1.412116527557373</v>
       </c>
       <c r="E46" t="n">
-        <v>1.342672824859619</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1.275674343109131</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1.507639646530151</v>
+        <v>1.342920064926147</v>
       </c>
     </row>
     <row r="47">
@@ -6789,19 +5499,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2.353135108947754</v>
+        <v>2.490448236465454</v>
       </c>
       <c r="D47" t="n">
-        <v>2.500156879425049</v>
+        <v>2.670268774032593</v>
       </c>
       <c r="E47" t="n">
-        <v>2.135392665863037</v>
-      </c>
-      <c r="F47" t="n">
-        <v>2.633859395980835</v>
-      </c>
-      <c r="G47" t="n">
-        <v>2.51220178604126</v>
+        <v>2.381153106689453</v>
       </c>
     </row>
     <row r="48">
@@ -6814,19 +5518,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.122150421142578</v>
+        <v>2.050222396850586</v>
       </c>
       <c r="D48" t="n">
-        <v>2.456222295761108</v>
+        <v>2.098424911499023</v>
       </c>
       <c r="E48" t="n">
-        <v>1.411986827850342</v>
-      </c>
-      <c r="F48" t="n">
-        <v>1.388794183731079</v>
-      </c>
-      <c r="G48" t="n">
-        <v>1.466156244277954</v>
+        <v>2.187233209609985</v>
       </c>
     </row>
     <row r="49">
@@ -6839,19 +5537,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.995573759078979</v>
+        <v>1.243442296981812</v>
       </c>
       <c r="D49" t="n">
-        <v>2.611328840255737</v>
+        <v>1.287861347198486</v>
       </c>
       <c r="E49" t="n">
-        <v>2.657893896102905</v>
-      </c>
-      <c r="F49" t="n">
-        <v>2.119318008422852</v>
-      </c>
-      <c r="G49" t="n">
-        <v>2.510068893432617</v>
+        <v>1.151381254196167</v>
       </c>
     </row>
     <row r="50">
@@ -6864,19 +5556,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.296047210693359</v>
+        <v>2.29468822479248</v>
       </c>
       <c r="D50" t="n">
-        <v>1.199195861816406</v>
+        <v>1.22198748588562</v>
       </c>
       <c r="E50" t="n">
-        <v>1.332285165786743</v>
-      </c>
-      <c r="F50" t="n">
-        <v>1.381855487823486</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1.281717777252197</v>
+        <v>2.406628847122192</v>
       </c>
     </row>
     <row r="51">
@@ -6889,19 +5575,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2.600600481033325</v>
+        <v>1.251818656921387</v>
       </c>
       <c r="D51" t="n">
-        <v>2.339927911758423</v>
+        <v>1.324367046356201</v>
       </c>
       <c r="E51" t="n">
-        <v>1.392815828323364</v>
-      </c>
-      <c r="F51" t="n">
-        <v>2.563252210617065</v>
-      </c>
-      <c r="G51" t="n">
-        <v>2.327001571655273</v>
+        <v>1.270624160766602</v>
       </c>
     </row>
     <row r="52">
@@ -6914,19 +5594,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.28794264793396</v>
+        <v>1.284340381622314</v>
       </c>
       <c r="D52" t="n">
-        <v>1.394148826599121</v>
+        <v>1.342004299163818</v>
       </c>
       <c r="E52" t="n">
-        <v>1.420061588287354</v>
-      </c>
-      <c r="F52" t="n">
-        <v>2.179286003112793</v>
-      </c>
-      <c r="G52" t="n">
-        <v>2.599456548690796</v>
+        <v>1.365970373153687</v>
       </c>
     </row>
     <row r="53">
@@ -6939,19 +5613,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.341248750686646</v>
+        <v>1.84688925743103</v>
       </c>
       <c r="D53" t="n">
-        <v>1.319059610366821</v>
+        <v>1.31590747833252</v>
       </c>
       <c r="E53" t="n">
-        <v>1.434843301773071</v>
-      </c>
-      <c r="F53" t="n">
-        <v>1.268665313720703</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1.34316873550415</v>
+        <v>1.920908212661743</v>
       </c>
     </row>
     <row r="54">
@@ -6964,19 +5632,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.423893928527832</v>
+        <v>1.412168264389038</v>
       </c>
       <c r="D54" t="n">
-        <v>1.398441553115845</v>
+        <v>1.438794136047363</v>
       </c>
       <c r="E54" t="n">
-        <v>1.513037443161011</v>
-      </c>
-      <c r="F54" t="n">
-        <v>1.445490598678589</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1.278618097305298</v>
+        <v>1.274997711181641</v>
       </c>
     </row>
     <row r="55">
@@ -6989,19 +5651,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.399616479873657</v>
+        <v>1.448718547821045</v>
       </c>
       <c r="D55" t="n">
-        <v>1.424716711044312</v>
+        <v>1.367502689361572</v>
       </c>
       <c r="E55" t="n">
-        <v>1.526770830154419</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1.492057800292969</v>
-      </c>
-      <c r="G55" t="n">
-        <v>1.393356323242188</v>
+        <v>1.341556787490845</v>
       </c>
     </row>
     <row r="56">
@@ -7014,19 +5670,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.537169694900513</v>
+        <v>1.490329027175903</v>
       </c>
       <c r="D56" t="n">
-        <v>1.443921327590942</v>
+        <v>1.369567155838013</v>
       </c>
       <c r="E56" t="n">
-        <v>1.27969217300415</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1.435462713241577</v>
-      </c>
-      <c r="G56" t="n">
-        <v>1.639114856719971</v>
+        <v>1.317444562911987</v>
       </c>
     </row>
     <row r="57">
@@ -7039,19 +5689,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.412698984146118</v>
+        <v>1.257670402526855</v>
       </c>
       <c r="D57" t="n">
-        <v>1.529565334320068</v>
+        <v>1.322086811065674</v>
       </c>
       <c r="E57" t="n">
-        <v>1.280592918395996</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1.450907230377197</v>
-      </c>
-      <c r="G57" t="n">
-        <v>1.360254526138306</v>
+        <v>1.236797571182251</v>
       </c>
     </row>
     <row r="58">
@@ -7064,19 +5708,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.981961727142334</v>
+        <v>1.571676969528198</v>
       </c>
       <c r="D58" t="n">
-        <v>1.072688102722168</v>
+        <v>1.314927339553833</v>
       </c>
       <c r="E58" t="n">
-        <v>1.191379547119141</v>
-      </c>
-      <c r="F58" t="n">
-        <v>1.252076625823975</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1.011837244033813</v>
+        <v>0.9495794773101807</v>
       </c>
     </row>
     <row r="59">
@@ -7089,19 +5727,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.574772596359253</v>
+        <v>1.171584844589233</v>
       </c>
       <c r="D59" t="n">
-        <v>1.365449905395508</v>
+        <v>1.186009168624878</v>
       </c>
       <c r="E59" t="n">
-        <v>1.655490875244141</v>
-      </c>
-      <c r="F59" t="n">
-        <v>1.331057548522949</v>
-      </c>
-      <c r="G59" t="n">
-        <v>1.363857269287109</v>
+        <v>1.18270206451416</v>
       </c>
     </row>
     <row r="60">
@@ -7114,19 +5746,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.262446880340576</v>
+        <v>1.371825933456421</v>
       </c>
       <c r="D60" t="n">
-        <v>1.490326881408691</v>
+        <v>1.342164754867554</v>
       </c>
       <c r="E60" t="n">
-        <v>1.353999853134155</v>
-      </c>
-      <c r="F60" t="n">
-        <v>1.527340888977051</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1.377957105636597</v>
+        <v>1.387398481369019</v>
       </c>
     </row>
     <row r="61">
@@ -7139,19 +5765,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.453476667404175</v>
+        <v>1.435316562652588</v>
       </c>
       <c r="D61" t="n">
-        <v>1.541136503219604</v>
+        <v>1.368716716766357</v>
       </c>
       <c r="E61" t="n">
-        <v>1.294095516204834</v>
-      </c>
-      <c r="F61" t="n">
-        <v>1.338577032089233</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1.470772981643677</v>
+        <v>1.337084531784058</v>
       </c>
     </row>
     <row r="62">
@@ -7164,19 +5784,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2.342205762863159</v>
+        <v>2.199630737304688</v>
       </c>
       <c r="D62" t="n">
-        <v>1.3923659324646</v>
+        <v>2.162742137908936</v>
       </c>
       <c r="E62" t="n">
-        <v>1.318357706069946</v>
-      </c>
-      <c r="F62" t="n">
-        <v>2.538108587265015</v>
-      </c>
-      <c r="G62" t="n">
-        <v>1.242030143737793</v>
+        <v>2.17891526222229</v>
       </c>
     </row>
     <row r="63">
@@ -7189,19 +5803,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2.096755981445312</v>
+        <v>2.532618999481201</v>
       </c>
       <c r="D63" t="n">
-        <v>1.351799249649048</v>
+        <v>2.258282423019409</v>
       </c>
       <c r="E63" t="n">
-        <v>1.759897708892822</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1.758547306060791</v>
-      </c>
-      <c r="G63" t="n">
-        <v>2.044129848480225</v>
+        <v>2.333542108535767</v>
       </c>
     </row>
     <row r="64">
@@ -7214,19 +5822,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1.768975019454956</v>
+        <v>1.26413106918335</v>
       </c>
       <c r="D64" t="n">
-        <v>1.882726907730103</v>
+        <v>1.37950611114502</v>
       </c>
       <c r="E64" t="n">
-        <v>1.415302991867065</v>
-      </c>
-      <c r="F64" t="n">
-        <v>2.806386947631836</v>
-      </c>
-      <c r="G64" t="n">
-        <v>2.263869285583496</v>
+        <v>1.397281646728516</v>
       </c>
     </row>
     <row r="65">
@@ -7239,19 +5841,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2.018628597259521</v>
+        <v>1.162780523300171</v>
       </c>
       <c r="D65" t="n">
-        <v>1.243069410324097</v>
+        <v>1.145846128463745</v>
       </c>
       <c r="E65" t="n">
-        <v>1.328965425491333</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1.095334529876709</v>
-      </c>
-      <c r="G65" t="n">
-        <v>1.256667137145996</v>
+        <v>1.156058073043823</v>
       </c>
     </row>
     <row r="66">
@@ -7264,19 +5860,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1.38369345664978</v>
+        <v>1.396625757217407</v>
       </c>
       <c r="D66" t="n">
-        <v>1.435297727584839</v>
+        <v>1.458062410354614</v>
       </c>
       <c r="E66" t="n">
-        <v>1.583763599395752</v>
-      </c>
-      <c r="F66" t="n">
-        <v>1.509047508239746</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1.424065589904785</v>
+        <v>1.527328491210938</v>
       </c>
     </row>
     <row r="67">
@@ -7289,19 +5879,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1.433700323104858</v>
+        <v>1.464027881622314</v>
       </c>
       <c r="D67" t="n">
-        <v>1.451614856719971</v>
+        <v>1.260371208190918</v>
       </c>
       <c r="E67" t="n">
-        <v>1.454671144485474</v>
-      </c>
-      <c r="F67" t="n">
-        <v>1.403179168701172</v>
-      </c>
-      <c r="G67" t="n">
-        <v>1.504456520080566</v>
+        <v>1.430506229400635</v>
       </c>
     </row>
     <row r="68">
@@ -7314,19 +5898,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1.554669141769409</v>
+        <v>1.229261159896851</v>
       </c>
       <c r="D68" t="n">
-        <v>1.370485305786133</v>
+        <v>1.209362745285034</v>
       </c>
       <c r="E68" t="n">
-        <v>1.311974287033081</v>
-      </c>
-      <c r="F68" t="n">
-        <v>1.326571941375732</v>
-      </c>
-      <c r="G68" t="n">
-        <v>1.238389015197754</v>
+        <v>1.277515172958374</v>
       </c>
     </row>
     <row r="69">
@@ -7339,19 +5917,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1.31087327003479</v>
+        <v>1.393112421035767</v>
       </c>
       <c r="D69" t="n">
-        <v>1.287856340408325</v>
+        <v>1.286571741104126</v>
       </c>
       <c r="E69" t="n">
-        <v>1.422092437744141</v>
-      </c>
-      <c r="F69" t="n">
-        <v>1.545169115066528</v>
-      </c>
-      <c r="G69" t="n">
-        <v>1.289428234100342</v>
+        <v>1.555422306060791</v>
       </c>
     </row>
     <row r="70">
@@ -7364,19 +5936,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.522398471832275</v>
+        <v>1.369745492935181</v>
       </c>
       <c r="D70" t="n">
-        <v>1.435985565185547</v>
+        <v>1.173265933990479</v>
       </c>
       <c r="E70" t="n">
-        <v>1.341452360153198</v>
-      </c>
-      <c r="F70" t="n">
-        <v>1.49838924407959</v>
-      </c>
-      <c r="G70" t="n">
-        <v>1.433788299560547</v>
+        <v>1.30808687210083</v>
       </c>
     </row>
     <row r="71">
@@ -7389,19 +5955,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.638616800308228</v>
+        <v>2.025201559066772</v>
       </c>
       <c r="D71" t="n">
-        <v>1.509911775588989</v>
+        <v>2.206727743148804</v>
       </c>
       <c r="E71" t="n">
-        <v>1.868563175201416</v>
-      </c>
-      <c r="F71" t="n">
-        <v>2.081940889358521</v>
-      </c>
-      <c r="G71" t="n">
-        <v>1.689567089080811</v>
+        <v>2.02209997177124</v>
       </c>
     </row>
     <row r="72">
@@ -7414,19 +5974,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1.431911468505859</v>
+        <v>1.777130842208862</v>
       </c>
       <c r="D72" t="n">
-        <v>1.069648504257202</v>
+        <v>0.8532767295837402</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9551844596862793</v>
-      </c>
-      <c r="F72" t="n">
-        <v>1.221453428268433</v>
-      </c>
-      <c r="G72" t="n">
-        <v>1.568480253219604</v>
+        <v>1.820619821548462</v>
       </c>
     </row>
     <row r="73">
@@ -7439,19 +5993,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2.697503566741943</v>
+        <v>1.106428861618042</v>
       </c>
       <c r="D73" t="n">
-        <v>1.315170288085938</v>
+        <v>1.233968496322632</v>
       </c>
       <c r="E73" t="n">
-        <v>1.28712272644043</v>
-      </c>
-      <c r="F73" t="n">
-        <v>1.306550979614258</v>
-      </c>
-      <c r="G73" t="n">
-        <v>1.33228063583374</v>
+        <v>1.515778303146362</v>
       </c>
     </row>
     <row r="74">
@@ -7464,19 +6012,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1.253553867340088</v>
+        <v>1.289028167724609</v>
       </c>
       <c r="D74" t="n">
-        <v>1.173828840255737</v>
+        <v>1.198915719985962</v>
       </c>
       <c r="E74" t="n">
-        <v>1.216837406158447</v>
-      </c>
-      <c r="F74" t="n">
-        <v>1.528098344802856</v>
-      </c>
-      <c r="G74" t="n">
-        <v>1.607358455657959</v>
+        <v>1.208516120910645</v>
       </c>
     </row>
     <row r="75">
@@ -7489,19 +6031,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1.46465277671814</v>
+        <v>1.281643152236938</v>
       </c>
       <c r="D75" t="n">
-        <v>1.462569952011108</v>
+        <v>1.260950565338135</v>
       </c>
       <c r="E75" t="n">
-        <v>1.625037431716919</v>
-      </c>
-      <c r="F75" t="n">
-        <v>1.460662841796875</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1.385779619216919</v>
+        <v>1.275372743606567</v>
       </c>
     </row>
     <row r="76">
@@ -7514,19 +6050,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1.719785690307617</v>
+        <v>1.405318260192871</v>
       </c>
       <c r="D76" t="n">
-        <v>1.356672048568726</v>
+        <v>1.533103227615356</v>
       </c>
       <c r="E76" t="n">
-        <v>1.379755020141602</v>
-      </c>
-      <c r="F76" t="n">
-        <v>1.540359973907471</v>
-      </c>
-      <c r="G76" t="n">
-        <v>1.383387327194214</v>
+        <v>1.367957592010498</v>
       </c>
     </row>
     <row r="77">
@@ -7539,19 +6069,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.428023815155029</v>
+        <v>1.325083017349243</v>
       </c>
       <c r="D77" t="n">
-        <v>1.711610317230225</v>
+        <v>1.274381875991821</v>
       </c>
       <c r="E77" t="n">
-        <v>1.359963893890381</v>
-      </c>
-      <c r="F77" t="n">
-        <v>1.422482490539551</v>
-      </c>
-      <c r="G77" t="n">
-        <v>1.493542194366455</v>
+        <v>1.270103454589844</v>
       </c>
     </row>
     <row r="78">
@@ -7564,19 +6088,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.375845909118652</v>
+        <v>1.210831880569458</v>
       </c>
       <c r="D78" t="n">
-        <v>1.211991310119629</v>
+        <v>1.183145761489868</v>
       </c>
       <c r="E78" t="n">
-        <v>1.490496158599854</v>
-      </c>
-      <c r="F78" t="n">
-        <v>1.222677946090698</v>
-      </c>
-      <c r="G78" t="n">
-        <v>1.460404634475708</v>
+        <v>1.244333267211914</v>
       </c>
     </row>
     <row r="79">
@@ -7589,19 +6107,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1.395538806915283</v>
+        <v>1.412786245346069</v>
       </c>
       <c r="D79" t="n">
-        <v>1.436808824539185</v>
+        <v>1.353918790817261</v>
       </c>
       <c r="E79" t="n">
-        <v>1.36467432975769</v>
-      </c>
-      <c r="F79" t="n">
-        <v>1.32136344909668</v>
-      </c>
-      <c r="G79" t="n">
-        <v>1.290324687957764</v>
+        <v>1.358569860458374</v>
       </c>
     </row>
     <row r="80">
@@ -7614,19 +6126,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.265494108200073</v>
+        <v>1.238403558731079</v>
       </c>
       <c r="D80" t="n">
-        <v>1.341900825500488</v>
+        <v>1.255040168762207</v>
       </c>
       <c r="E80" t="n">
-        <v>1.203325510025024</v>
-      </c>
-      <c r="F80" t="n">
-        <v>1.398105621337891</v>
-      </c>
-      <c r="G80" t="n">
-        <v>1.483190059661865</v>
+        <v>1.261801481246948</v>
       </c>
     </row>
     <row r="81">
@@ -7639,19 +6145,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1.425239324569702</v>
+        <v>1.235460758209229</v>
       </c>
       <c r="D81" t="n">
-        <v>1.440697193145752</v>
+        <v>1.343405485153198</v>
       </c>
       <c r="E81" t="n">
-        <v>1.266859769821167</v>
-      </c>
-      <c r="F81" t="n">
-        <v>1.524863958358765</v>
-      </c>
-      <c r="G81" t="n">
-        <v>1.301253795623779</v>
+        <v>1.218398332595825</v>
       </c>
     </row>
     <row r="82">
@@ -7664,19 +6164,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1.566047430038452</v>
+        <v>1.323761224746704</v>
       </c>
       <c r="D82" t="n">
-        <v>1.488559484481812</v>
+        <v>1.358972549438477</v>
       </c>
       <c r="E82" t="n">
-        <v>1.785551309585571</v>
-      </c>
-      <c r="F82" t="n">
-        <v>1.477672100067139</v>
-      </c>
-      <c r="G82" t="n">
-        <v>1.392570495605469</v>
+        <v>1.236629247665405</v>
       </c>
     </row>
     <row r="83">
@@ -7689,19 +6183,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.520934343338013</v>
+        <v>1.188204526901245</v>
       </c>
       <c r="D83" t="n">
-        <v>1.284422397613525</v>
+        <v>1.228409290313721</v>
       </c>
       <c r="E83" t="n">
-        <v>1.499607563018799</v>
-      </c>
-      <c r="F83" t="n">
-        <v>1.291894435882568</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1.495730400085449</v>
+        <v>1.501385688781738</v>
       </c>
     </row>
     <row r="84">
@@ -7714,19 +6202,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1.676090002059937</v>
+        <v>1.363354682922363</v>
       </c>
       <c r="D84" t="n">
-        <v>1.335290193557739</v>
+        <v>1.352515697479248</v>
       </c>
       <c r="E84" t="n">
-        <v>1.667252063751221</v>
-      </c>
-      <c r="F84" t="n">
-        <v>1.315732955932617</v>
-      </c>
-      <c r="G84" t="n">
-        <v>1.382705688476562</v>
+        <v>1.278708457946777</v>
       </c>
     </row>
     <row r="85">
@@ -7739,19 +6221,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1.265993356704712</v>
+        <v>1.318658351898193</v>
       </c>
       <c r="D85" t="n">
-        <v>1.385435104370117</v>
+        <v>1.298871517181396</v>
       </c>
       <c r="E85" t="n">
-        <v>1.337332010269165</v>
-      </c>
-      <c r="F85" t="n">
-        <v>1.238695383071899</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1.274943113327026</v>
+        <v>1.226034641265869</v>
       </c>
     </row>
     <row r="86">
@@ -7764,19 +6240,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1.4296555519104</v>
+        <v>1.563235282897949</v>
       </c>
       <c r="D86" t="n">
-        <v>1.60463809967041</v>
+        <v>1.530942678451538</v>
       </c>
       <c r="E86" t="n">
-        <v>1.649068117141724</v>
-      </c>
-      <c r="F86" t="n">
-        <v>1.35372257232666</v>
-      </c>
-      <c r="G86" t="n">
-        <v>1.451565504074097</v>
+        <v>1.463274002075195</v>
       </c>
     </row>
     <row r="87">
@@ -7789,19 +6259,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.829100370407104</v>
+        <v>2.114398241043091</v>
       </c>
       <c r="D87" t="n">
-        <v>2.139517545700073</v>
+        <v>1.174381017684937</v>
       </c>
       <c r="E87" t="n">
-        <v>2.004273653030396</v>
-      </c>
-      <c r="F87" t="n">
-        <v>2.039236545562744</v>
-      </c>
-      <c r="G87" t="n">
-        <v>1.918087720870972</v>
+        <v>2.050781488418579</v>
       </c>
     </row>
     <row r="88">
@@ -7814,19 +6278,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1.406295299530029</v>
+        <v>1.272399663925171</v>
       </c>
       <c r="D88" t="n">
-        <v>1.34697413444519</v>
+        <v>1.497351408004761</v>
       </c>
       <c r="E88" t="n">
-        <v>1.291369676589966</v>
-      </c>
-      <c r="F88" t="n">
-        <v>1.211562156677246</v>
-      </c>
-      <c r="G88" t="n">
-        <v>1.538308382034302</v>
+        <v>1.265592098236084</v>
       </c>
     </row>
     <row r="89">
@@ -7839,19 +6297,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1.5989089012146</v>
+        <v>1.359697103500366</v>
       </c>
       <c r="D89" t="n">
-        <v>1.546993255615234</v>
+        <v>1.363803386688232</v>
       </c>
       <c r="E89" t="n">
-        <v>1.56126070022583</v>
-      </c>
-      <c r="F89" t="n">
-        <v>1.563806533813477</v>
-      </c>
-      <c r="G89" t="n">
-        <v>1.720906257629395</v>
+        <v>1.36266040802002</v>
       </c>
     </row>
     <row r="90">
@@ -7864,19 +6316,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1.252631902694702</v>
+        <v>1.488475799560547</v>
       </c>
       <c r="D90" t="n">
-        <v>1.360764265060425</v>
+        <v>1.323538541793823</v>
       </c>
       <c r="E90" t="n">
-        <v>1.28224515914917</v>
-      </c>
-      <c r="F90" t="n">
-        <v>1.172945022583008</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1.188849925994873</v>
+        <v>1.189974308013916</v>
       </c>
     </row>
     <row r="91">
@@ -7889,19 +6335,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1.457898616790771</v>
+        <v>1.459551572799683</v>
       </c>
       <c r="D91" t="n">
-        <v>1.443823575973511</v>
+        <v>1.412827968597412</v>
       </c>
       <c r="E91" t="n">
-        <v>1.383873462677002</v>
-      </c>
-      <c r="F91" t="n">
-        <v>1.608140468597412</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1.289729118347168</v>
+        <v>1.311456441879272</v>
       </c>
     </row>
     <row r="92">
@@ -7914,19 +6354,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1.33675479888916</v>
+        <v>1.374194622039795</v>
       </c>
       <c r="D92" t="n">
-        <v>1.445266008377075</v>
+        <v>1.312065124511719</v>
       </c>
       <c r="E92" t="n">
-        <v>1.330100297927856</v>
-      </c>
-      <c r="F92" t="n">
-        <v>1.85599160194397</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1.574253082275391</v>
+        <v>1.370953321456909</v>
       </c>
     </row>
     <row r="93">
@@ -7939,19 +6373,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1.16729474067688</v>
+        <v>1.24583911895752</v>
       </c>
       <c r="D93" t="n">
-        <v>1.362561941146851</v>
+        <v>1.417254447937012</v>
       </c>
       <c r="E93" t="n">
-        <v>1.203489065170288</v>
-      </c>
-      <c r="F93" t="n">
-        <v>1.165573596954346</v>
-      </c>
-      <c r="G93" t="n">
-        <v>1.55677318572998</v>
+        <v>1.330177068710327</v>
       </c>
     </row>
     <row r="94">
@@ -7964,19 +6392,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1.445724010467529</v>
+        <v>1.502983570098877</v>
       </c>
       <c r="D94" t="n">
-        <v>1.493558406829834</v>
+        <v>1.614649295806885</v>
       </c>
       <c r="E94" t="n">
-        <v>1.673959732055664</v>
-      </c>
-      <c r="F94" t="n">
-        <v>1.68564772605896</v>
-      </c>
-      <c r="G94" t="n">
-        <v>1.546417713165283</v>
+        <v>1.516680479049683</v>
       </c>
     </row>
     <row r="95">
@@ -7989,19 +6411,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1.561708211898804</v>
+        <v>1.367849588394165</v>
       </c>
       <c r="D95" t="n">
-        <v>1.331047773361206</v>
+        <v>1.350142240524292</v>
       </c>
       <c r="E95" t="n">
-        <v>1.504742860794067</v>
-      </c>
-      <c r="F95" t="n">
-        <v>1.862741947174072</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1.321129083633423</v>
+        <v>1.373937606811523</v>
       </c>
     </row>
     <row r="96">
@@ -8014,19 +6430,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1.340508699417114</v>
+        <v>1.419476985931396</v>
       </c>
       <c r="D96" t="n">
-        <v>1.455856084823608</v>
+        <v>1.357412338256836</v>
       </c>
       <c r="E96" t="n">
-        <v>1.310131072998047</v>
-      </c>
-      <c r="F96" t="n">
-        <v>1.491450309753418</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1.502137660980225</v>
+        <v>1.409060716629028</v>
       </c>
     </row>
     <row r="97">
@@ -8039,19 +6449,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1.28380274772644</v>
+        <v>1.726734399795532</v>
       </c>
       <c r="D97" t="n">
-        <v>1.196651935577393</v>
+        <v>1.96172833442688</v>
       </c>
       <c r="E97" t="n">
-        <v>1.150570631027222</v>
-      </c>
-      <c r="F97" t="n">
-        <v>1.283976554870605</v>
-      </c>
-      <c r="G97" t="n">
-        <v>1.204334497451782</v>
+        <v>1.780316829681396</v>
       </c>
     </row>
     <row r="98">
@@ -8064,19 +6468,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1.466970443725586</v>
+        <v>1.494749307632446</v>
       </c>
       <c r="D98" t="n">
-        <v>1.428942203521729</v>
+        <v>1.375519275665283</v>
       </c>
       <c r="E98" t="n">
-        <v>1.424278974533081</v>
-      </c>
-      <c r="F98" t="n">
-        <v>1.276216268539429</v>
-      </c>
-      <c r="G98" t="n">
-        <v>1.366118669509888</v>
+        <v>1.306811571121216</v>
       </c>
     </row>
     <row r="99">
@@ -8089,19 +6487,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1.347497463226318</v>
+        <v>1.293332576751709</v>
       </c>
       <c r="D99" t="n">
-        <v>1.259335517883301</v>
+        <v>1.244698762893677</v>
       </c>
       <c r="E99" t="n">
-        <v>1.204102277755737</v>
-      </c>
-      <c r="F99" t="n">
-        <v>1.200120210647583</v>
-      </c>
-      <c r="G99" t="n">
-        <v>1.350611209869385</v>
+        <v>1.214709281921387</v>
       </c>
     </row>
     <row r="100">
@@ -8114,19 +6506,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1.129260063171387</v>
+        <v>1.211328744888306</v>
       </c>
       <c r="D100" t="n">
-        <v>1.233240127563477</v>
+        <v>1.27665638923645</v>
       </c>
       <c r="E100" t="n">
-        <v>1.381506681442261</v>
-      </c>
-      <c r="F100" t="n">
-        <v>1.192344427108765</v>
-      </c>
-      <c r="G100" t="n">
-        <v>1.793523073196411</v>
+        <v>1.248379230499268</v>
       </c>
     </row>
     <row r="101">
@@ -8139,19 +6525,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1.283724308013916</v>
+        <v>1.448461055755615</v>
       </c>
       <c r="D101" t="n">
-        <v>1.639660358428955</v>
+        <v>1.314961671829224</v>
       </c>
       <c r="E101" t="n">
-        <v>1.306350946426392</v>
-      </c>
-      <c r="F101" t="n">
-        <v>1.381590843200684</v>
-      </c>
-      <c r="G101" t="n">
-        <v>1.591769456863403</v>
+        <v>1.334123373031616</v>
       </c>
     </row>
   </sheetData>
